--- a/research/traditional_assets/database/data/argentina/argentina_shoe.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_shoe.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2233442288134256</v>
+        <v>0.2225917740125787</v>
       </c>
       <c r="C2">
-        <v>67.37465912936035</v>
+        <v>66.94788017856204</v>
       </c>
       <c r="D2">
-        <v>66.93365912936035</v>
+        <v>67.17798017856204</v>
       </c>
       <c r="E2">
-        <v>-8.01</v>
+        <v>-7.3389</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.6711</v>
       </c>
       <c r="G2">
         <v>0.441</v>
@@ -1445,28 +1445,28 @@
         <v>21.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.03375633</v>
       </c>
       <c r="N2">
-        <v>21.9</v>
+        <v>21.86624367</v>
       </c>
       <c r="O2">
-        <v>7.664999999999999</v>
+        <v>7.653185284499999</v>
       </c>
       <c r="P2">
-        <v>14.235</v>
+        <v>14.2130583855</v>
       </c>
       <c r="Q2">
-        <v>15.035</v>
+        <v>15.0130583855</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2233442288134256</v>
+        <v>0.2245099232450289</v>
       </c>
       <c r="T2">
-        <v>0.8723408754896529</v>
+        <v>0.8780683660863022</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>648.7672089945796</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2225917740125787</v>
+        <v>0.2218393192117316</v>
       </c>
       <c r="C3">
-        <v>66.94788017856204</v>
+        <v>66.52289140222943</v>
       </c>
       <c r="D3">
-        <v>67.17798017856204</v>
+        <v>67.42409140222944</v>
       </c>
       <c r="E3">
-        <v>-7.3389</v>
+        <v>-6.6678</v>
       </c>
       <c r="F3">
-        <v>0.6711</v>
+        <v>1.3422</v>
       </c>
       <c r="G3">
         <v>0.441</v>
@@ -1527,28 +1527,28 @@
         <v>21.9</v>
       </c>
       <c r="M3">
-        <v>0.03375633</v>
+        <v>0.06751266</v>
       </c>
       <c r="N3">
-        <v>21.86624367</v>
+        <v>21.83248734</v>
       </c>
       <c r="O3">
-        <v>7.653185284499999</v>
+        <v>7.641370568999999</v>
       </c>
       <c r="P3">
-        <v>14.2130583855</v>
+        <v>14.191116771</v>
       </c>
       <c r="Q3">
-        <v>15.0130583855</v>
+        <v>14.991116771</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2245099232450289</v>
+        <v>0.2256994073589098</v>
       </c>
       <c r="T3">
-        <v>0.8780683660863022</v>
+        <v>0.8839127442461483</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>648.7672089945796</v>
+        <v>324.3836044972898</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2218393192117316</v>
+        <v>0.2210868644108847</v>
       </c>
       <c r="C4">
-        <v>66.52289140222943</v>
+        <v>66.09971254799706</v>
       </c>
       <c r="D4">
-        <v>67.42409140222944</v>
+        <v>67.67201254799706</v>
       </c>
       <c r="E4">
-        <v>-6.6678</v>
+        <v>-5.9967</v>
       </c>
       <c r="F4">
-        <v>1.3422</v>
+        <v>2.0133</v>
       </c>
       <c r="G4">
         <v>0.441</v>
@@ -1609,28 +1609,28 @@
         <v>21.9</v>
       </c>
       <c r="M4">
-        <v>0.06751266</v>
+        <v>0.10126899</v>
       </c>
       <c r="N4">
-        <v>21.83248734</v>
+        <v>21.79873101</v>
       </c>
       <c r="O4">
-        <v>7.641370568999999</v>
+        <v>7.629555853499999</v>
       </c>
       <c r="P4">
-        <v>14.191116771</v>
+        <v>14.1691751565</v>
       </c>
       <c r="Q4">
-        <v>14.991116771</v>
+        <v>14.9691751565</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2256994073589098</v>
+        <v>0.2269134169184378</v>
       </c>
       <c r="T4">
-        <v>0.8839127442461483</v>
+        <v>0.8898776250484655</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>324.3836044972898</v>
+        <v>216.2557363315265</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2210868644108847</v>
+        <v>0.2203344096100376</v>
       </c>
       <c r="C5">
-        <v>66.09971254799706</v>
+        <v>65.67836365502278</v>
       </c>
       <c r="D5">
-        <v>67.67201254799706</v>
+        <v>67.92176365502277</v>
       </c>
       <c r="E5">
-        <v>-5.9967</v>
+        <v>-5.3256</v>
       </c>
       <c r="F5">
-        <v>2.0133</v>
+        <v>2.6844</v>
       </c>
       <c r="G5">
         <v>0.441</v>
@@ -1691,28 +1691,28 @@
         <v>21.9</v>
       </c>
       <c r="M5">
-        <v>0.10126899</v>
+        <v>0.13502532</v>
       </c>
       <c r="N5">
-        <v>21.79873101</v>
+        <v>21.76497468</v>
       </c>
       <c r="O5">
-        <v>7.629555853499999</v>
+        <v>7.617741137999999</v>
       </c>
       <c r="P5">
-        <v>14.1691751565</v>
+        <v>14.147233542</v>
       </c>
       <c r="Q5">
-        <v>14.9691751565</v>
+        <v>14.947233542</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2269134169184378</v>
+        <v>0.2281527183437892</v>
       </c>
       <c r="T5">
-        <v>0.8898776250484655</v>
+        <v>0.895966774200831</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>216.2557363315265</v>
+        <v>162.1918022486449</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2203344096100376</v>
+        <v>0.2195819548091907</v>
       </c>
       <c r="C6">
-        <v>65.67836365502278</v>
+        <v>65.25886505938732</v>
       </c>
       <c r="D6">
-        <v>67.92176365502277</v>
+        <v>68.17336505938732</v>
       </c>
       <c r="E6">
-        <v>-5.3256</v>
+        <v>-4.6545</v>
       </c>
       <c r="F6">
-        <v>2.6844</v>
+        <v>3.3555</v>
       </c>
       <c r="G6">
         <v>0.441</v>
@@ -1773,28 +1773,28 @@
         <v>21.9</v>
       </c>
       <c r="M6">
-        <v>0.13502532</v>
+        <v>0.16878165</v>
       </c>
       <c r="N6">
-        <v>21.76497468</v>
+        <v>21.73121835</v>
       </c>
       <c r="O6">
-        <v>7.617741137999999</v>
+        <v>7.605926422499999</v>
       </c>
       <c r="P6">
-        <v>14.147233542</v>
+        <v>14.1252919275</v>
       </c>
       <c r="Q6">
-        <v>14.947233542</v>
+        <v>14.9252919275</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2281527183437892</v>
+        <v>0.2294181103254639</v>
       </c>
       <c r="T6">
-        <v>0.895966774200831</v>
+        <v>0.9021841159669305</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>162.1918022486449</v>
+        <v>129.7534417989159</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2195819548091907</v>
+        <v>0.2188295000083437</v>
       </c>
       <c r="C7">
-        <v>65.25886505938732</v>
+        <v>64.84123739961406</v>
       </c>
       <c r="D7">
-        <v>68.17336505938732</v>
+        <v>68.42683739961406</v>
       </c>
       <c r="E7">
-        <v>-4.6545</v>
+        <v>-3.9834</v>
       </c>
       <c r="F7">
-        <v>3.3555</v>
+        <v>4.0266</v>
       </c>
       <c r="G7">
         <v>0.441</v>
@@ -1855,28 +1855,28 @@
         <v>21.9</v>
       </c>
       <c r="M7">
-        <v>0.16878165</v>
+        <v>0.20253798</v>
       </c>
       <c r="N7">
-        <v>21.73121835</v>
+        <v>21.69746202</v>
       </c>
       <c r="O7">
-        <v>7.605926422499999</v>
+        <v>7.594111707</v>
       </c>
       <c r="P7">
-        <v>14.1252919275</v>
+        <v>14.103350313</v>
       </c>
       <c r="Q7">
-        <v>14.9252919275</v>
+        <v>14.903350313</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2294181103254639</v>
+        <v>0.2307104255407911</v>
       </c>
       <c r="T7">
-        <v>0.9021841159669305</v>
+        <v>0.9085337416003938</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>129.7534417989159</v>
+        <v>108.1278681657633</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2188295000083437</v>
+        <v>0.2180770452074967</v>
       </c>
       <c r="C8">
-        <v>64.84123739961406</v>
+        <v>64.42550162231258</v>
       </c>
       <c r="D8">
-        <v>68.42683739961406</v>
+        <v>68.68220162231258</v>
       </c>
       <c r="E8">
-        <v>-3.9834</v>
+        <v>-3.3123</v>
       </c>
       <c r="F8">
-        <v>4.0266</v>
+        <v>4.697699999999999</v>
       </c>
       <c r="G8">
         <v>0.441</v>
@@ -1937,28 +1937,28 @@
         <v>21.9</v>
       </c>
       <c r="M8">
-        <v>0.20253798</v>
+        <v>0.23629431</v>
       </c>
       <c r="N8">
-        <v>21.69746202</v>
+        <v>21.66370569</v>
       </c>
       <c r="O8">
-        <v>7.594111707</v>
+        <v>7.582296991499998</v>
       </c>
       <c r="P8">
-        <v>14.103350313</v>
+        <v>14.0814086985</v>
       </c>
       <c r="Q8">
-        <v>14.903350313</v>
+        <v>14.8814086985</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2307104255407911</v>
+        <v>0.2320305324811792</v>
       </c>
       <c r="T8">
-        <v>0.9085337416003938</v>
+        <v>0.9150199183227488</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>108.1278681657633</v>
+        <v>92.68102985636853</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2180770452074967</v>
+        <v>0.2173245904066497</v>
       </c>
       <c r="C9">
-        <v>64.42550162231259</v>
+        <v>64.01167898794893</v>
       </c>
       <c r="D9">
-        <v>68.68220162231259</v>
+        <v>68.93947898794892</v>
       </c>
       <c r="E9">
-        <v>-3.3123</v>
+        <v>-2.6412</v>
       </c>
       <c r="F9">
-        <v>4.6977</v>
+        <v>5.3688</v>
       </c>
       <c r="G9">
         <v>0.441</v>
@@ -2019,28 +2019,28 @@
         <v>21.9</v>
       </c>
       <c r="M9">
-        <v>0.23629431</v>
+        <v>0.27005064</v>
       </c>
       <c r="N9">
-        <v>21.66370569</v>
+        <v>21.62994936</v>
       </c>
       <c r="O9">
-        <v>7.582296991499998</v>
+        <v>7.570482275999999</v>
       </c>
       <c r="P9">
-        <v>14.0814086985</v>
+        <v>14.059467084</v>
       </c>
       <c r="Q9">
-        <v>14.8814086985</v>
+        <v>14.859467084</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2320305324811792</v>
+        <v>0.2333793373985323</v>
       </c>
       <c r="T9">
-        <v>0.9150199183227488</v>
+        <v>0.921647098886894</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>92.68102985636851</v>
+        <v>81.09590112432245</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2173245904066497</v>
+        <v>0.2165721356058027</v>
       </c>
       <c r="C10">
-        <v>64.01167898794893</v>
+        <v>63.59979107674609</v>
       </c>
       <c r="D10">
-        <v>68.93947898794892</v>
+        <v>69.19869107674609</v>
       </c>
       <c r="E10">
-        <v>-2.6412</v>
+        <v>-1.9701</v>
       </c>
       <c r="F10">
-        <v>5.3688</v>
+        <v>6.039899999999999</v>
       </c>
       <c r="G10">
         <v>0.441</v>
@@ -2101,28 +2101,28 @@
         <v>21.9</v>
       </c>
       <c r="M10">
-        <v>0.27005064</v>
+        <v>0.30380697</v>
       </c>
       <c r="N10">
-        <v>21.62994936</v>
+        <v>21.59619303</v>
       </c>
       <c r="O10">
-        <v>7.570482275999999</v>
+        <v>7.558667560499999</v>
       </c>
       <c r="P10">
-        <v>14.059467084</v>
+        <v>14.0375254695</v>
       </c>
       <c r="Q10">
-        <v>14.859467084</v>
+        <v>14.8375254695</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2333793373985323</v>
+        <v>0.234757786380003</v>
       </c>
       <c r="T10">
-        <v>0.921647098886894</v>
+        <v>0.9284199317711306</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>81.09590112432245</v>
+        <v>72.0852454438422</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2165721356058027</v>
+        <v>0.2158196808049557</v>
       </c>
       <c r="C11">
-        <v>63.59979107674609</v>
+        <v>63.18985979471817</v>
       </c>
       <c r="D11">
-        <v>69.19869107674609</v>
+        <v>69.45985979471817</v>
       </c>
       <c r="E11">
-        <v>-1.9701</v>
+        <v>-1.299</v>
       </c>
       <c r="F11">
-        <v>6.039899999999999</v>
+        <v>6.710999999999999</v>
       </c>
       <c r="G11">
         <v>0.441</v>
@@ -2183,28 +2183,28 @@
         <v>21.9</v>
       </c>
       <c r="M11">
-        <v>0.30380697</v>
+        <v>0.3375633</v>
       </c>
       <c r="N11">
-        <v>21.59619303</v>
+        <v>21.5624367</v>
       </c>
       <c r="O11">
-        <v>7.558667560499999</v>
+        <v>7.546852844999999</v>
       </c>
       <c r="P11">
-        <v>14.0375254695</v>
+        <v>14.015583855</v>
       </c>
       <c r="Q11">
-        <v>14.8375254695</v>
+        <v>14.815583855</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.234757786380003</v>
+        <v>0.2361668675610619</v>
       </c>
       <c r="T11">
-        <v>0.9284199317711306</v>
+        <v>0.9353432720527944</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>72.0852454438422</v>
+        <v>64.87672089945798</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2158196808049557</v>
+        <v>0.2150672260041087</v>
       </c>
       <c r="C12">
-        <v>63.18985979471817</v>
+        <v>62.78190737984168</v>
       </c>
       <c r="D12">
-        <v>69.45985979471817</v>
+        <v>69.72300737984168</v>
       </c>
       <c r="E12">
-        <v>-1.298999999999999</v>
+        <v>-0.6278999999999995</v>
       </c>
       <c r="F12">
-        <v>6.711</v>
+        <v>7.3821</v>
       </c>
       <c r="G12">
         <v>0.441</v>
@@ -2265,28 +2265,28 @@
         <v>21.9</v>
       </c>
       <c r="M12">
-        <v>0.3375633</v>
+        <v>0.37131963</v>
       </c>
       <c r="N12">
-        <v>21.5624367</v>
+        <v>21.52868037</v>
       </c>
       <c r="O12">
-        <v>7.546852844999999</v>
+        <v>7.535038129499999</v>
       </c>
       <c r="P12">
-        <v>14.015583855</v>
+        <v>13.9936422405</v>
       </c>
       <c r="Q12">
-        <v>14.815583855</v>
+        <v>14.7936422405</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2361668675610619</v>
+        <v>0.2376076134877626</v>
       </c>
       <c r="T12">
-        <v>0.9353432720527944</v>
+        <v>0.9424221930149453</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>64.87672089945796</v>
+        <v>58.97883718132542</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2150672260041087</v>
+        <v>0.2143147712032617</v>
       </c>
       <c r="C13">
-        <v>62.78190737984168</v>
+        <v>62.37595640836747</v>
       </c>
       <c r="D13">
-        <v>69.72300737984168</v>
+        <v>69.98815640836747</v>
       </c>
       <c r="E13">
-        <v>-0.6278999999999995</v>
+        <v>0.04320000000000057</v>
       </c>
       <c r="F13">
-        <v>7.3821</v>
+        <v>8.0532</v>
       </c>
       <c r="G13">
         <v>0.441</v>
@@ -2347,28 +2347,28 @@
         <v>21.9</v>
       </c>
       <c r="M13">
-        <v>0.37131963</v>
+        <v>0.40507596</v>
       </c>
       <c r="N13">
-        <v>21.52868037</v>
+        <v>21.49492404</v>
       </c>
       <c r="O13">
-        <v>7.535038129499999</v>
+        <v>7.523223413999998</v>
       </c>
       <c r="P13">
-        <v>13.9936422405</v>
+        <v>13.971700626</v>
       </c>
       <c r="Q13">
-        <v>14.7936422405</v>
+        <v>14.771700626</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2376076134877626</v>
+        <v>0.2390811036400702</v>
       </c>
       <c r="T13">
-        <v>0.9424221930149453</v>
+        <v>0.9496619985444176</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>58.97883718132542</v>
+        <v>54.06393408288163</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2143147712032617</v>
+        <v>0.2135623164024147</v>
       </c>
       <c r="C14">
-        <v>62.37595640836747</v>
+        <v>61.97202980127757</v>
       </c>
       <c r="D14">
-        <v>69.98815640836747</v>
+        <v>70.25532980127757</v>
       </c>
       <c r="E14">
-        <v>0.04320000000000057</v>
+        <v>0.7142999999999997</v>
       </c>
       <c r="F14">
-        <v>8.0532</v>
+        <v>8.724299999999999</v>
       </c>
       <c r="G14">
         <v>0.441</v>
@@ -2429,28 +2429,28 @@
         <v>21.9</v>
       </c>
       <c r="M14">
-        <v>0.40507596</v>
+        <v>0.43883229</v>
       </c>
       <c r="N14">
-        <v>21.49492404</v>
+        <v>21.46116771</v>
       </c>
       <c r="O14">
-        <v>7.523223413999998</v>
+        <v>7.511408698499999</v>
       </c>
       <c r="P14">
-        <v>13.971700626</v>
+        <v>13.9497590115</v>
       </c>
       <c r="Q14">
-        <v>14.771700626</v>
+        <v>14.7497590115</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2390811036400702</v>
+        <v>0.2405884671292123</v>
       </c>
       <c r="T14">
-        <v>0.9496619985444176</v>
+        <v>0.9570682363849122</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>54.06393408288163</v>
+        <v>49.90516992265997</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2135623164024147</v>
+        <v>0.2128098616015678</v>
       </c>
       <c r="C15">
-        <v>61.97202980127757</v>
+        <v>61.57015083089019</v>
       </c>
       <c r="D15">
-        <v>70.25532980127757</v>
+        <v>70.52455083089019</v>
       </c>
       <c r="E15">
-        <v>0.7142999999999997</v>
+        <v>1.385400000000001</v>
       </c>
       <c r="F15">
-        <v>8.724299999999999</v>
+        <v>9.3954</v>
       </c>
       <c r="G15">
         <v>0.441</v>
@@ -2511,28 +2511,28 @@
         <v>21.9</v>
       </c>
       <c r="M15">
-        <v>0.43883229</v>
+        <v>0.47258862</v>
       </c>
       <c r="N15">
-        <v>21.46116771</v>
+        <v>21.42741138</v>
       </c>
       <c r="O15">
-        <v>7.511408698499999</v>
+        <v>7.499593982999999</v>
       </c>
       <c r="P15">
-        <v>13.9497590115</v>
+        <v>13.927817397</v>
       </c>
       <c r="Q15">
-        <v>14.7497590115</v>
+        <v>14.727817397</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2405884671292123</v>
+        <v>0.2421308855832183</v>
       </c>
       <c r="T15">
-        <v>0.9570682363849122</v>
+        <v>0.9646467123147209</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>49.90516992265997</v>
+        <v>46.34051492818426</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2128098616015678</v>
+        <v>0.2120574068007208</v>
       </c>
       <c r="C16">
-        <v>61.57015083089019</v>
+        <v>61.17034312761731</v>
       </c>
       <c r="D16">
-        <v>70.52455083089019</v>
+        <v>70.79584312761732</v>
       </c>
       <c r="E16">
-        <v>1.385400000000001</v>
+        <v>2.056500000000002</v>
       </c>
       <c r="F16">
-        <v>9.3954</v>
+        <v>10.0665</v>
       </c>
       <c r="G16">
         <v>0.441</v>
@@ -2593,28 +2593,28 @@
         <v>21.9</v>
       </c>
       <c r="M16">
-        <v>0.47258862</v>
+        <v>0.50634495</v>
       </c>
       <c r="N16">
-        <v>21.42741138</v>
+        <v>21.39365505</v>
       </c>
       <c r="O16">
-        <v>7.499593982999999</v>
+        <v>7.4877792675</v>
       </c>
       <c r="P16">
-        <v>13.927817397</v>
+        <v>13.9058757825</v>
       </c>
       <c r="Q16">
-        <v>14.727817397</v>
+        <v>14.7058757825</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2421308855832183</v>
+        <v>0.2437095962361421</v>
       </c>
       <c r="T16">
-        <v>0.9646467123147209</v>
+        <v>0.9724035053252308</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>46.34051492818426</v>
+        <v>43.25114726630531</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2120574068007208</v>
+        <v>0.2113049519998738</v>
       </c>
       <c r="C17">
-        <v>61.17034312761732</v>
+        <v>60.77263068687886</v>
       </c>
       <c r="D17">
-        <v>70.79584312761732</v>
+        <v>71.06923068687885</v>
       </c>
       <c r="E17">
-        <v>2.0565</v>
+        <v>2.727600000000001</v>
       </c>
       <c r="F17">
-        <v>10.0665</v>
+        <v>10.7376</v>
       </c>
       <c r="G17">
         <v>0.441</v>
@@ -2675,28 +2675,28 @@
         <v>21.9</v>
       </c>
       <c r="M17">
-        <v>0.5063449499999999</v>
+        <v>0.54010128</v>
       </c>
       <c r="N17">
-        <v>21.39365505</v>
+        <v>21.35989872</v>
       </c>
       <c r="O17">
-        <v>7.4877792675</v>
+        <v>7.475964551999998</v>
       </c>
       <c r="P17">
-        <v>13.9058757825</v>
+        <v>13.883934168</v>
       </c>
       <c r="Q17">
-        <v>14.7058757825</v>
+        <v>14.683934168</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2437095962361421</v>
+        <v>0.245325895237945</v>
       </c>
       <c r="T17">
-        <v>0.9724035053252308</v>
+        <v>0.9803449838836099</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>43.25114726630532</v>
+        <v>40.54795056216123</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2113049519998738</v>
+        <v>0.2105524971990268</v>
       </c>
       <c r="C18">
-        <v>60.77263068687886</v>
+        <v>60.37703787617757</v>
       </c>
       <c r="D18">
-        <v>71.06923068687885</v>
+        <v>71.34473787617758</v>
       </c>
       <c r="E18">
-        <v>2.727600000000001</v>
+        <v>3.398700000000002</v>
       </c>
       <c r="F18">
-        <v>10.7376</v>
+        <v>11.4087</v>
       </c>
       <c r="G18">
         <v>0.441</v>
@@ -2757,28 +2757,28 @@
         <v>21.9</v>
       </c>
       <c r="M18">
-        <v>0.54010128</v>
+        <v>0.57385761</v>
       </c>
       <c r="N18">
-        <v>21.35989872</v>
+        <v>21.32614239</v>
       </c>
       <c r="O18">
-        <v>7.475964551999998</v>
+        <v>7.464149836499999</v>
       </c>
       <c r="P18">
-        <v>13.883934168</v>
+        <v>13.8619925535</v>
       </c>
       <c r="Q18">
-        <v>14.683934168</v>
+        <v>14.6619925535</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.245325895237945</v>
+        <v>0.2469811412036467</v>
       </c>
       <c r="T18">
-        <v>0.9803449838836099</v>
+        <v>0.9884778233711067</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>40.54795056216123</v>
+        <v>38.16277699968115</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2105524971990268</v>
+        <v>0.2098000423981798</v>
       </c>
       <c r="C19">
-        <v>60.37703787617757</v>
+        <v>59.98358944233924</v>
       </c>
       <c r="D19">
-        <v>71.34473787617758</v>
+        <v>71.62238944233924</v>
       </c>
       <c r="E19">
-        <v>3.398700000000002</v>
+        <v>4.069800000000001</v>
       </c>
       <c r="F19">
-        <v>11.4087</v>
+        <v>12.0798</v>
       </c>
       <c r="G19">
         <v>0.441</v>
@@ -2839,28 +2839,28 @@
         <v>21.9</v>
       </c>
       <c r="M19">
-        <v>0.57385761</v>
+        <v>0.60761394</v>
       </c>
       <c r="N19">
-        <v>21.32614239</v>
+        <v>21.29238606</v>
       </c>
       <c r="O19">
-        <v>7.464149836499999</v>
+        <v>7.452335120999999</v>
       </c>
       <c r="P19">
-        <v>13.8619925535</v>
+        <v>13.840050939</v>
       </c>
       <c r="Q19">
-        <v>14.6619925535</v>
+        <v>14.640050939</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2469811412036467</v>
+        <v>0.2486767590221705</v>
       </c>
       <c r="T19">
-        <v>0.9884778233711067</v>
+        <v>0.9968090247973228</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>38.16277699968115</v>
+        <v>36.04262272192109</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2098000423981798</v>
+        <v>0.2090475875973328</v>
       </c>
       <c r="C20">
-        <v>59.98358944233924</v>
+        <v>59.59231051892253</v>
       </c>
       <c r="D20">
-        <v>71.62238944233924</v>
+        <v>71.90221051892253</v>
       </c>
       <c r="E20">
-        <v>4.069799999999999</v>
+        <v>4.7409</v>
       </c>
       <c r="F20">
-        <v>12.0798</v>
+        <v>12.7509</v>
       </c>
       <c r="G20">
         <v>0.441</v>
@@ -2921,28 +2921,28 @@
         <v>21.9</v>
       </c>
       <c r="M20">
-        <v>0.6076139399999999</v>
+        <v>0.6413702699999999</v>
       </c>
       <c r="N20">
-        <v>21.29238606</v>
+        <v>21.25862973</v>
       </c>
       <c r="O20">
-        <v>7.452335120999999</v>
+        <v>7.440520405499999</v>
       </c>
       <c r="P20">
-        <v>13.840050939</v>
+        <v>13.8181093245</v>
       </c>
       <c r="Q20">
-        <v>14.640050939</v>
+        <v>14.6181093245</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2486767590221705</v>
+        <v>0.2504142439473244</v>
       </c>
       <c r="T20">
-        <v>0.9968090247973228</v>
+        <v>1.00534593490073</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>36.0426227219211</v>
+        <v>34.14564257866209</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2090475875973328</v>
+        <v>0.2082951327964858</v>
       </c>
       <c r="C21">
-        <v>59.59231051892253</v>
+        <v>59.20322663380325</v>
       </c>
       <c r="D21">
-        <v>71.90221051892253</v>
+        <v>72.18422663380325</v>
       </c>
       <c r="E21">
-        <v>4.7409</v>
+        <v>5.412000000000001</v>
       </c>
       <c r="F21">
-        <v>12.7509</v>
+        <v>13.422</v>
       </c>
       <c r="G21">
         <v>0.441</v>
@@ -3003,28 +3003,28 @@
         <v>21.9</v>
       </c>
       <c r="M21">
-        <v>0.6413702699999999</v>
+        <v>0.6751266</v>
       </c>
       <c r="N21">
-        <v>21.25862973</v>
+        <v>21.2248734</v>
       </c>
       <c r="O21">
-        <v>7.440520405499999</v>
+        <v>7.428705689999999</v>
       </c>
       <c r="P21">
-        <v>13.8181093245</v>
+        <v>13.79616771</v>
       </c>
       <c r="Q21">
-        <v>14.6181093245</v>
+        <v>14.59616771</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2504142439473244</v>
+        <v>0.2521951659956073</v>
       </c>
       <c r="T21">
-        <v>1.00534593490073</v>
+        <v>1.014096267756722</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>34.14564257866209</v>
+        <v>32.43836044972898</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2082951327964858</v>
+        <v>0.2075426779956388</v>
       </c>
       <c r="C22">
-        <v>59.20322663380325</v>
+        <v>58.81636371693782</v>
       </c>
       <c r="D22">
-        <v>72.18422663380325</v>
+        <v>72.46846371693782</v>
       </c>
       <c r="E22">
-        <v>5.412000000000001</v>
+        <v>6.083100000000002</v>
       </c>
       <c r="F22">
-        <v>13.422</v>
+        <v>14.0931</v>
       </c>
       <c r="G22">
         <v>0.441</v>
@@ -3085,28 +3085,28 @@
         <v>21.9</v>
       </c>
       <c r="M22">
-        <v>0.6751266</v>
+        <v>0.70888293</v>
       </c>
       <c r="N22">
-        <v>21.2248734</v>
+        <v>21.19111707</v>
       </c>
       <c r="O22">
-        <v>7.428705689999999</v>
+        <v>7.416890974499998</v>
       </c>
       <c r="P22">
-        <v>13.79616771</v>
+        <v>13.7742260955</v>
       </c>
       <c r="Q22">
-        <v>14.59616771</v>
+        <v>14.5742260955</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2521951659956073</v>
+        <v>0.2540211746780238</v>
       </c>
       <c r="T22">
-        <v>1.014096267756722</v>
+        <v>1.023068128026789</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>32.43836044972898</v>
+        <v>30.8936766187895</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2075426779956388</v>
+        <v>0.2067902231947918</v>
       </c>
       <c r="C23">
-        <v>58.81636371693782</v>
+        <v>58.43174810831079</v>
       </c>
       <c r="D23">
-        <v>72.46846371693782</v>
+        <v>72.75494810831078</v>
       </c>
       <c r="E23">
-        <v>6.0831</v>
+        <v>6.754200000000001</v>
       </c>
       <c r="F23">
-        <v>14.0931</v>
+        <v>14.7642</v>
       </c>
       <c r="G23">
         <v>0.441</v>
@@ -3167,28 +3167,28 @@
         <v>21.9</v>
       </c>
       <c r="M23">
-        <v>0.7088829299999999</v>
+        <v>0.74263926</v>
       </c>
       <c r="N23">
-        <v>21.19111707</v>
+        <v>21.15736074</v>
       </c>
       <c r="O23">
-        <v>7.416890974499998</v>
+        <v>7.405076258999999</v>
       </c>
       <c r="P23">
-        <v>13.7742260955</v>
+        <v>13.752284481</v>
       </c>
       <c r="Q23">
-        <v>14.5742260955</v>
+        <v>14.552284481</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2540211746780238</v>
+        <v>0.255894004095887</v>
       </c>
       <c r="T23">
-        <v>1.023068128026789</v>
+        <v>1.032270035996089</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>30.89367661878951</v>
+        <v>29.48941859066271</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2067902231947918</v>
+        <v>0.2060377683939449</v>
       </c>
       <c r="C24">
-        <v>58.43174810831079</v>
+        <v>58.0494065660717</v>
       </c>
       <c r="D24">
-        <v>72.75494810831078</v>
+        <v>73.04370656607169</v>
       </c>
       <c r="E24">
-        <v>6.754200000000001</v>
+        <v>7.4253</v>
       </c>
       <c r="F24">
-        <v>14.7642</v>
+        <v>15.4353</v>
       </c>
       <c r="G24">
         <v>0.441</v>
@@ -3249,28 +3249,28 @@
         <v>21.9</v>
       </c>
       <c r="M24">
-        <v>0.74263926</v>
+        <v>0.7763955899999999</v>
       </c>
       <c r="N24">
-        <v>21.15736074</v>
+        <v>21.12360441</v>
       </c>
       <c r="O24">
-        <v>7.405076258999999</v>
+        <v>7.393261543499999</v>
       </c>
       <c r="P24">
-        <v>13.752284481</v>
+        <v>13.7303428665</v>
       </c>
       <c r="Q24">
-        <v>14.552284481</v>
+        <v>14.5303428665</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.255894004095887</v>
+        <v>0.2578154784336946</v>
       </c>
       <c r="T24">
-        <v>1.032270035996089</v>
+        <v>1.041710954561995</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>29.48941859066271</v>
+        <v>28.20726995628608</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2060377683939449</v>
+        <v>0.2052853135930979</v>
       </c>
       <c r="C25">
-        <v>58.0494065660717</v>
+        <v>57.66936627486653</v>
       </c>
       <c r="D25">
-        <v>73.04370656607169</v>
+        <v>73.33476627486652</v>
       </c>
       <c r="E25">
-        <v>7.4253</v>
+        <v>8.096400000000001</v>
       </c>
       <c r="F25">
-        <v>15.4353</v>
+        <v>16.1064</v>
       </c>
       <c r="G25">
         <v>0.441</v>
@@ -3331,28 +3331,28 @@
         <v>21.9</v>
       </c>
       <c r="M25">
-        <v>0.7763955899999999</v>
+        <v>0.81015192</v>
       </c>
       <c r="N25">
-        <v>21.12360441</v>
+        <v>21.08984808</v>
       </c>
       <c r="O25">
-        <v>7.393261543499999</v>
+        <v>7.381446828</v>
       </c>
       <c r="P25">
-        <v>13.7303428665</v>
+        <v>13.708401252</v>
       </c>
       <c r="Q25">
-        <v>14.5303428665</v>
+        <v>14.508401252</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2578154784336946</v>
+        <v>0.2597875178856551</v>
       </c>
       <c r="T25">
-        <v>1.041710954561995</v>
+        <v>1.051400318353318</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>28.20726995628608</v>
+        <v>27.03196704144082</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2052853135930979</v>
+        <v>0.2045328587922509</v>
       </c>
       <c r="C26">
-        <v>57.66936627486653</v>
+        <v>57.29165485436897</v>
       </c>
       <c r="D26">
-        <v>73.33476627486652</v>
+        <v>73.62815485436897</v>
       </c>
       <c r="E26">
-        <v>8.096400000000001</v>
+        <v>8.7675</v>
       </c>
       <c r="F26">
-        <v>16.1064</v>
+        <v>16.7775</v>
       </c>
       <c r="G26">
         <v>0.441</v>
@@ -3413,28 +3413,28 @@
         <v>21.9</v>
       </c>
       <c r="M26">
-        <v>0.81015192</v>
+        <v>0.8439082499999999</v>
       </c>
       <c r="N26">
-        <v>21.08984808</v>
+        <v>21.05609175</v>
       </c>
       <c r="O26">
-        <v>7.381446828</v>
+        <v>7.3696321125</v>
       </c>
       <c r="P26">
-        <v>13.708401252</v>
+        <v>13.6864596375</v>
       </c>
       <c r="Q26">
-        <v>14.508401252</v>
+        <v>14.4864596375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2597875178856551</v>
+        <v>0.2618121450563345</v>
       </c>
       <c r="T26">
-        <v>1.051400318353318</v>
+        <v>1.061348065179078</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>27.03196704144082</v>
+        <v>25.95068835978319</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2045328587922509</v>
+        <v>0.2037804039914039</v>
       </c>
       <c r="C27">
-        <v>57.29165485436897</v>
+        <v>56.91630036801749</v>
       </c>
       <c r="D27">
-        <v>73.62815485436897</v>
+        <v>73.92390036801748</v>
       </c>
       <c r="E27">
-        <v>8.7675</v>
+        <v>9.438599999999999</v>
       </c>
       <c r="F27">
-        <v>16.7775</v>
+        <v>17.4486</v>
       </c>
       <c r="G27">
         <v>0.441</v>
@@ -3495,28 +3495,28 @@
         <v>21.9</v>
       </c>
       <c r="M27">
-        <v>0.8439082499999999</v>
+        <v>0.8776645799999999</v>
       </c>
       <c r="N27">
-        <v>21.05609175</v>
+        <v>21.02233542</v>
       </c>
       <c r="O27">
-        <v>7.3696321125</v>
+        <v>7.357817396999999</v>
       </c>
       <c r="P27">
-        <v>13.6864596375</v>
+        <v>13.664518023</v>
       </c>
       <c r="Q27">
-        <v>14.4864596375</v>
+        <v>14.464518023</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2618121450563345</v>
+        <v>0.2638914918802755</v>
       </c>
       <c r="T27">
-        <v>1.061348065179078</v>
+        <v>1.071564670027155</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>25.95068835978319</v>
+        <v>24.95258496132999</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2037804039914039</v>
+        <v>0.2030279491905569</v>
       </c>
       <c r="C28">
-        <v>56.91630036801749</v>
+        <v>56.54333133196359</v>
       </c>
       <c r="D28">
-        <v>73.92390036801748</v>
+        <v>74.22203133196359</v>
       </c>
       <c r="E28">
-        <v>9.438599999999999</v>
+        <v>10.1097</v>
       </c>
       <c r="F28">
-        <v>17.4486</v>
+        <v>18.1197</v>
       </c>
       <c r="G28">
         <v>0.441</v>
@@ -3577,28 +3577,28 @@
         <v>21.9</v>
       </c>
       <c r="M28">
-        <v>0.8776645799999999</v>
+        <v>0.91142091</v>
       </c>
       <c r="N28">
-        <v>21.02233542</v>
+        <v>20.98857909</v>
       </c>
       <c r="O28">
-        <v>7.357817396999999</v>
+        <v>7.346002681499999</v>
       </c>
       <c r="P28">
-        <v>13.664518023</v>
+        <v>13.6425764085</v>
       </c>
       <c r="Q28">
-        <v>14.464518023</v>
+        <v>14.4425764085</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2638914918802755</v>
+        <v>0.2660278071103519</v>
       </c>
       <c r="T28">
-        <v>1.071564670027155</v>
+        <v>1.082061181857371</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>24.95258496132999</v>
+        <v>24.02841514794739</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2030279491905569</v>
+        <v>0.2022754943897099</v>
       </c>
       <c r="C29">
-        <v>56.54333133196359</v>
+        <v>56.17277672423781</v>
       </c>
       <c r="D29">
-        <v>74.22203133196359</v>
+        <v>74.52257672423781</v>
       </c>
       <c r="E29">
-        <v>10.1097</v>
+        <v>10.7808</v>
       </c>
       <c r="F29">
-        <v>18.1197</v>
+        <v>18.7908</v>
       </c>
       <c r="G29">
         <v>0.441</v>
@@ -3659,28 +3659,28 @@
         <v>21.9</v>
       </c>
       <c r="M29">
-        <v>0.91142091</v>
+        <v>0.94517724</v>
       </c>
       <c r="N29">
-        <v>20.98857909</v>
+        <v>20.95482276</v>
       </c>
       <c r="O29">
-        <v>7.346002681499999</v>
+        <v>7.334187965999999</v>
       </c>
       <c r="P29">
-        <v>13.6425764085</v>
+        <v>13.620634794</v>
       </c>
       <c r="Q29">
-        <v>14.4425764085</v>
+        <v>14.420634794</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2660278071103519</v>
+        <v>0.2682234644301526</v>
       </c>
       <c r="T29">
-        <v>1.082061181857371</v>
+        <v>1.092849263460648</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>24.02841514794739</v>
+        <v>23.17025746409213</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2022754943897099</v>
+        <v>0.2015230395888629</v>
       </c>
       <c r="C30">
-        <v>56.17277672423781</v>
+        <v>55.8046659941389</v>
       </c>
       <c r="D30">
-        <v>74.52257672423781</v>
+        <v>74.8255659941389</v>
       </c>
       <c r="E30">
-        <v>10.7808</v>
+        <v>11.4519</v>
       </c>
       <c r="F30">
-        <v>18.7908</v>
+        <v>19.4619</v>
       </c>
       <c r="G30">
         <v>0.441</v>
@@ -3741,28 +3741,28 @@
         <v>21.9</v>
       </c>
       <c r="M30">
-        <v>0.94517724</v>
+        <v>0.9789335700000001</v>
       </c>
       <c r="N30">
-        <v>20.95482276</v>
+        <v>20.92106643</v>
       </c>
       <c r="O30">
-        <v>7.334187965999999</v>
+        <v>7.322373250499999</v>
       </c>
       <c r="P30">
-        <v>13.620634794</v>
+        <v>13.5986931795</v>
       </c>
       <c r="Q30">
-        <v>14.420634794</v>
+        <v>14.3986931795</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2682234644301526</v>
+        <v>0.2704809712519196</v>
       </c>
       <c r="T30">
-        <v>1.092849263460648</v>
+        <v>1.103941234686554</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>23.17025746409213</v>
+        <v>22.37128306877861</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2015230395888629</v>
+        <v>0.2007705847880159</v>
       </c>
       <c r="C31">
-        <v>55.8046659941389</v>
+        <v>55.43902907185338</v>
       </c>
       <c r="D31">
-        <v>74.8255659941389</v>
+        <v>75.13102907185338</v>
       </c>
       <c r="E31">
-        <v>11.4519</v>
+        <v>12.123</v>
       </c>
       <c r="F31">
-        <v>19.4619</v>
+        <v>20.133</v>
       </c>
       <c r="G31">
         <v>0.441</v>
@@ -3823,28 +3823,28 @@
         <v>21.9</v>
       </c>
       <c r="M31">
-        <v>0.9789335699999999</v>
+        <v>1.0126899</v>
       </c>
       <c r="N31">
-        <v>20.92106643</v>
+        <v>20.8873101</v>
       </c>
       <c r="O31">
-        <v>7.322373250499999</v>
+        <v>7.310558534999999</v>
       </c>
       <c r="P31">
-        <v>13.5986931795</v>
+        <v>13.576751565</v>
       </c>
       <c r="Q31">
-        <v>14.3986931795</v>
+        <v>14.376751565</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2704809712519196</v>
+        <v>0.2728029782685942</v>
       </c>
       <c r="T31">
-        <v>1.103941234686554</v>
+        <v>1.115350119376056</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>22.37128306877861</v>
+        <v>21.62557363315266</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2007705847880159</v>
+        <v>0.2000181299871689</v>
       </c>
       <c r="C32">
-        <v>55.43902907185338</v>
+        <v>55.07589637831139</v>
       </c>
       <c r="D32">
-        <v>75.13102907185338</v>
+        <v>75.43899637831139</v>
       </c>
       <c r="E32">
-        <v>12.123</v>
+        <v>12.7941</v>
       </c>
       <c r="F32">
-        <v>20.133</v>
+        <v>20.8041</v>
       </c>
       <c r="G32">
         <v>0.441</v>
@@ -3905,28 +3905,28 @@
         <v>21.9</v>
       </c>
       <c r="M32">
-        <v>1.0126899</v>
+        <v>1.04644623</v>
       </c>
       <c r="N32">
-        <v>20.8873101</v>
+        <v>20.85355377</v>
       </c>
       <c r="O32">
-        <v>7.310558534999999</v>
+        <v>7.298743819499999</v>
       </c>
       <c r="P32">
-        <v>13.576751565</v>
+        <v>13.5548099505</v>
       </c>
       <c r="Q32">
-        <v>14.376751565</v>
+        <v>14.3548099505</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2728029782685942</v>
+        <v>0.2751922898364767</v>
       </c>
       <c r="T32">
-        <v>1.115350119376056</v>
+        <v>1.127089696375399</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>21.62557363315266</v>
+        <v>20.92797448369612</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2000181299871689</v>
+        <v>0.1992656751863219</v>
       </c>
       <c r="C33">
-        <v>55.07589637831139</v>
+        <v>54.71529883528603</v>
       </c>
       <c r="D33">
-        <v>75.43899637831139</v>
+        <v>75.74949883528603</v>
       </c>
       <c r="E33">
-        <v>12.7941</v>
+        <v>13.4652</v>
       </c>
       <c r="F33">
-        <v>20.8041</v>
+        <v>21.4752</v>
       </c>
       <c r="G33">
         <v>0.441</v>
@@ -3987,28 +3987,28 @@
         <v>21.9</v>
       </c>
       <c r="M33">
-        <v>1.04644623</v>
+        <v>1.08020256</v>
       </c>
       <c r="N33">
-        <v>20.85355377</v>
+        <v>20.81979744</v>
       </c>
       <c r="O33">
-        <v>7.298743819499999</v>
+        <v>7.286929103999999</v>
       </c>
       <c r="P33">
-        <v>13.5548099505</v>
+        <v>13.532868336</v>
       </c>
       <c r="Q33">
-        <v>14.3548099505</v>
+        <v>14.332868336</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2751922898364767</v>
+        <v>0.2776518752740029</v>
       </c>
       <c r="T33">
-        <v>1.127089696375399</v>
+        <v>1.139174555051194</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>20.92797448369612</v>
+        <v>20.27397528108061</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1992656751863219</v>
+        <v>0.1985132203854749</v>
       </c>
       <c r="C34">
-        <v>54.71529883528603</v>
+        <v>54.3572678757434</v>
       </c>
       <c r="D34">
-        <v>75.74949883528603</v>
+        <v>76.0625678757434</v>
       </c>
       <c r="E34">
-        <v>13.4652</v>
+        <v>14.1363</v>
       </c>
       <c r="F34">
-        <v>21.4752</v>
+        <v>22.1463</v>
       </c>
       <c r="G34">
         <v>0.441</v>
@@ -4069,28 +4069,28 @@
         <v>21.9</v>
       </c>
       <c r="M34">
-        <v>1.08020256</v>
+        <v>1.11395889</v>
       </c>
       <c r="N34">
-        <v>20.81979744</v>
+        <v>20.78604111</v>
       </c>
       <c r="O34">
-        <v>7.286929103999999</v>
+        <v>7.2751143885</v>
       </c>
       <c r="P34">
-        <v>13.532868336</v>
+        <v>13.5109267215</v>
       </c>
       <c r="Q34">
-        <v>14.332868336</v>
+        <v>14.3109267215</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2776518752740029</v>
+        <v>0.2801848811723506</v>
       </c>
       <c r="T34">
-        <v>1.139174555051194</v>
+        <v>1.151620155777012</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>20.27397528108061</v>
+        <v>19.65961239377514</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1985132203854749</v>
+        <v>0.1977607655846279</v>
       </c>
       <c r="C35">
-        <v>54.3572678757434</v>
+        <v>54.00183545444965</v>
       </c>
       <c r="D35">
-        <v>76.0625678757434</v>
+        <v>76.37823545444965</v>
       </c>
       <c r="E35">
-        <v>14.1363</v>
+        <v>14.8074</v>
       </c>
       <c r="F35">
-        <v>22.1463</v>
+        <v>22.8174</v>
       </c>
       <c r="G35">
         <v>0.441</v>
@@ -4151,28 +4151,28 @@
         <v>21.9</v>
       </c>
       <c r="M35">
-        <v>1.11395889</v>
+        <v>1.14771522</v>
       </c>
       <c r="N35">
-        <v>20.78604111</v>
+        <v>20.75228478</v>
       </c>
       <c r="O35">
-        <v>7.2751143885</v>
+        <v>7.263299673</v>
       </c>
       <c r="P35">
-        <v>13.5109267215</v>
+        <v>13.488985107</v>
       </c>
       <c r="Q35">
-        <v>14.3109267215</v>
+        <v>14.288985107</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2801848811723506</v>
+        <v>0.2827946448251939</v>
       </c>
       <c r="T35">
-        <v>1.151620155777012</v>
+        <v>1.164442895918764</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>19.65961239377514</v>
+        <v>19.08138849984058</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1977607655846279</v>
+        <v>0.1970083107837809</v>
       </c>
       <c r="C36">
-        <v>54.00183545444965</v>
+        <v>53.64903405884424</v>
       </c>
       <c r="D36">
-        <v>76.37823545444965</v>
+        <v>76.69653405884424</v>
       </c>
       <c r="E36">
-        <v>14.8074</v>
+        <v>15.4785</v>
       </c>
       <c r="F36">
-        <v>22.8174</v>
+        <v>23.4885</v>
       </c>
       <c r="G36">
         <v>0.441</v>
@@ -4233,28 +4233,28 @@
         <v>21.9</v>
       </c>
       <c r="M36">
-        <v>1.14771522</v>
+        <v>1.18147155</v>
       </c>
       <c r="N36">
-        <v>20.75228478</v>
+        <v>20.71852845</v>
       </c>
       <c r="O36">
-        <v>7.263299673</v>
+        <v>7.251484957499999</v>
       </c>
       <c r="P36">
-        <v>13.488985107</v>
+        <v>13.4670434925</v>
       </c>
       <c r="Q36">
-        <v>14.288985107</v>
+        <v>14.2670434925</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2827946448251939</v>
+        <v>0.2854847088981246</v>
       </c>
       <c r="T36">
-        <v>1.164442895918764</v>
+        <v>1.177660181911032</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>19.08138849984058</v>
+        <v>18.5362059712737</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1970083107837809</v>
+        <v>0.196255855982934</v>
       </c>
       <c r="C37">
-        <v>53.64903405884424</v>
+        <v>53.29889672018538</v>
       </c>
       <c r="D37">
-        <v>76.69653405884424</v>
+        <v>77.01749672018538</v>
       </c>
       <c r="E37">
-        <v>15.4785</v>
+        <v>16.1496</v>
       </c>
       <c r="F37">
-        <v>23.4885</v>
+        <v>24.1596</v>
       </c>
       <c r="G37">
         <v>0.441</v>
@@ -4315,28 +4315,28 @@
         <v>21.9</v>
       </c>
       <c r="M37">
-        <v>1.18147155</v>
+        <v>1.21522788</v>
       </c>
       <c r="N37">
-        <v>20.71852845</v>
+        <v>20.68477212</v>
       </c>
       <c r="O37">
-        <v>7.251484957499999</v>
+        <v>7.239670241999999</v>
       </c>
       <c r="P37">
-        <v>13.4670434925</v>
+        <v>13.445101878</v>
       </c>
       <c r="Q37">
-        <v>14.2670434925</v>
+        <v>14.245101878</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2854847088981246</v>
+        <v>0.2882588374733344</v>
       </c>
       <c r="T37">
-        <v>1.177660181911032</v>
+        <v>1.191290508090557</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>18.5362059712737</v>
+        <v>18.02131136096055</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.196255855982934</v>
+        <v>0.1955034011820869</v>
       </c>
       <c r="C38">
-        <v>53.29889672018537</v>
+        <v>52.95145702497692</v>
       </c>
       <c r="D38">
-        <v>77.01749672018536</v>
+        <v>77.34115702497692</v>
       </c>
       <c r="E38">
-        <v>16.1496</v>
+        <v>16.8207</v>
       </c>
       <c r="F38">
-        <v>24.1596</v>
+        <v>24.8307</v>
       </c>
       <c r="G38">
         <v>0.441</v>
@@ -4397,28 +4397,28 @@
         <v>21.9</v>
       </c>
       <c r="M38">
-        <v>1.21522788</v>
+        <v>1.24898421</v>
       </c>
       <c r="N38">
-        <v>20.68477212</v>
+        <v>20.65101579</v>
       </c>
       <c r="O38">
-        <v>7.239670241999999</v>
+        <v>7.227855526499999</v>
       </c>
       <c r="P38">
-        <v>13.445101878</v>
+        <v>13.4231602635</v>
       </c>
       <c r="Q38">
-        <v>14.245101878</v>
+        <v>14.2231602635</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2882588374733344</v>
+        <v>0.2911210336223602</v>
       </c>
       <c r="T38">
-        <v>1.191290508090557</v>
+        <v>1.205353543037687</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>18.02131136096055</v>
+        <v>17.5342488917454</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1955034011820869</v>
+        <v>0.19475094638124</v>
       </c>
       <c r="C39">
-        <v>52.95145702497692</v>
+        <v>52.60674912668443</v>
       </c>
       <c r="D39">
-        <v>77.34115702497692</v>
+        <v>77.66754912668443</v>
       </c>
       <c r="E39">
-        <v>16.8207</v>
+        <v>17.4918</v>
       </c>
       <c r="F39">
-        <v>24.8307</v>
+        <v>25.5018</v>
       </c>
       <c r="G39">
         <v>0.441</v>
@@ -4479,28 +4479,28 @@
         <v>21.9</v>
       </c>
       <c r="M39">
-        <v>1.24898421</v>
+        <v>1.28274054</v>
       </c>
       <c r="N39">
-        <v>20.65101579</v>
+        <v>20.61725946</v>
       </c>
       <c r="O39">
-        <v>7.227855526499999</v>
+        <v>7.216040810999999</v>
       </c>
       <c r="P39">
-        <v>13.4231602635</v>
+        <v>13.401218649</v>
       </c>
       <c r="Q39">
-        <v>14.2231602635</v>
+        <v>14.201218649</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2911210336223602</v>
+        <v>0.2940755586794194</v>
       </c>
       <c r="T39">
-        <v>1.205353543037687</v>
+        <v>1.219870224273434</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>17.5342488917454</v>
+        <v>17.07282128933105</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.19475094638124</v>
+        <v>0.193998491580393</v>
       </c>
       <c r="C40">
-        <v>52.60674912668443</v>
+        <v>52.26480775774937</v>
       </c>
       <c r="D40">
-        <v>77.66754912668443</v>
+        <v>77.99670775774936</v>
       </c>
       <c r="E40">
-        <v>17.4918</v>
+        <v>18.1629</v>
       </c>
       <c r="F40">
-        <v>25.5018</v>
+        <v>26.1729</v>
       </c>
       <c r="G40">
         <v>0.441</v>
@@ -4561,28 +4561,28 @@
         <v>21.9</v>
       </c>
       <c r="M40">
-        <v>1.28274054</v>
+        <v>1.31649687</v>
       </c>
       <c r="N40">
-        <v>20.61725946</v>
+        <v>20.58350313</v>
       </c>
       <c r="O40">
-        <v>7.216040810999999</v>
+        <v>7.204226095499998</v>
       </c>
       <c r="P40">
-        <v>13.401218649</v>
+        <v>13.3792770345</v>
       </c>
       <c r="Q40">
-        <v>14.201218649</v>
+        <v>14.1792770345</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2940755586794194</v>
+        <v>0.2971269534104803</v>
       </c>
       <c r="T40">
-        <v>1.219870224273434</v>
+        <v>1.234862862271009</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>17.07282128933105</v>
+        <v>16.63505664088666</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.193998491580393</v>
+        <v>0.193246036779546</v>
       </c>
       <c r="C41">
-        <v>52.26480775774937</v>
+        <v>51.92566824190978</v>
       </c>
       <c r="D41">
-        <v>77.99670775774936</v>
+        <v>78.32866824190978</v>
       </c>
       <c r="E41">
-        <v>18.1629</v>
+        <v>18.834</v>
       </c>
       <c r="F41">
-        <v>26.1729</v>
+        <v>26.844</v>
       </c>
       <c r="G41">
         <v>0.441</v>
@@ -4643,28 +4643,28 @@
         <v>21.9</v>
       </c>
       <c r="M41">
-        <v>1.31649687</v>
+        <v>1.3502532</v>
       </c>
       <c r="N41">
-        <v>20.58350313</v>
+        <v>20.5497468</v>
       </c>
       <c r="O41">
-        <v>7.204226095499998</v>
+        <v>7.192411379999998</v>
       </c>
       <c r="P41">
-        <v>13.3792770345</v>
+        <v>13.35733542</v>
       </c>
       <c r="Q41">
-        <v>14.1792770345</v>
+        <v>14.15733542</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2971269534104803</v>
+        <v>0.3002800612992433</v>
       </c>
       <c r="T41">
-        <v>1.234862862271009</v>
+        <v>1.250355254868502</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>16.63505664088666</v>
+        <v>16.21918022486449</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.193246036779546</v>
+        <v>0.192493581978699</v>
       </c>
       <c r="C42">
-        <v>51.92566824190978</v>
+        <v>51.58936650683719</v>
       </c>
       <c r="D42">
-        <v>78.32866824190978</v>
+        <v>78.6634665068372</v>
       </c>
       <c r="E42">
-        <v>18.834</v>
+        <v>19.5051</v>
       </c>
       <c r="F42">
-        <v>26.844</v>
+        <v>27.5151</v>
       </c>
       <c r="G42">
         <v>0.441</v>
@@ -4725,28 +4725,28 @@
         <v>21.9</v>
       </c>
       <c r="M42">
-        <v>1.3502532</v>
+        <v>1.38400953</v>
       </c>
       <c r="N42">
-        <v>20.5497468</v>
+        <v>20.51599047</v>
       </c>
       <c r="O42">
-        <v>7.192411379999998</v>
+        <v>7.180596664499999</v>
       </c>
       <c r="P42">
-        <v>13.35733542</v>
+        <v>13.3353938055</v>
       </c>
       <c r="Q42">
-        <v>14.15733542</v>
+        <v>14.1353938055</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3002800612992433</v>
+        <v>0.3035400542011848</v>
       </c>
       <c r="T42">
-        <v>1.250355254868502</v>
+        <v>1.266372813316759</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>16.21918022486449</v>
+        <v>15.82359046328243</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.192493581978699</v>
+        <v>0.191741127177852</v>
       </c>
       <c r="C43">
-        <v>51.58936650683719</v>
+        <v>51.25593909709895</v>
       </c>
       <c r="D43">
-        <v>78.6634665068372</v>
+        <v>79.00113909709894</v>
       </c>
       <c r="E43">
-        <v>19.5051</v>
+        <v>20.1762</v>
       </c>
       <c r="F43">
-        <v>27.5151</v>
+        <v>28.1862</v>
       </c>
       <c r="G43">
         <v>0.441</v>
@@ -4807,28 +4807,28 @@
         <v>21.9</v>
       </c>
       <c r="M43">
-        <v>1.38400953</v>
+        <v>1.41776586</v>
       </c>
       <c r="N43">
-        <v>20.51599047</v>
+        <v>20.48223414</v>
       </c>
       <c r="O43">
-        <v>7.180596664499999</v>
+        <v>7.168781949</v>
       </c>
       <c r="P43">
-        <v>13.3353938055</v>
+        <v>13.313452191</v>
       </c>
       <c r="Q43">
-        <v>14.1353938055</v>
+        <v>14.113452191</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3035400542011848</v>
+        <v>0.306912460651469</v>
       </c>
       <c r="T43">
-        <v>1.266372813316759</v>
+        <v>1.282942701366679</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>15.82359046328243</v>
+        <v>15.44683830939475</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.191741127177852</v>
+        <v>0.1909886723770051</v>
       </c>
       <c r="C44">
-        <v>51.25593909709893</v>
+        <v>50.92542318745566</v>
       </c>
       <c r="D44">
-        <v>79.00113909709893</v>
+        <v>79.34172318745566</v>
       </c>
       <c r="E44">
-        <v>20.1762</v>
+        <v>20.8473</v>
       </c>
       <c r="F44">
-        <v>28.1862</v>
+        <v>28.8573</v>
       </c>
       <c r="G44">
         <v>0.441</v>
@@ -4889,28 +4889,28 @@
         <v>21.9</v>
       </c>
       <c r="M44">
-        <v>1.41776586</v>
+        <v>1.45152219</v>
       </c>
       <c r="N44">
-        <v>20.48223414</v>
+        <v>20.44847781</v>
       </c>
       <c r="O44">
-        <v>7.168781949</v>
+        <v>7.1569672335</v>
       </c>
       <c r="P44">
-        <v>13.313452191</v>
+        <v>13.2915105765</v>
       </c>
       <c r="Q44">
-        <v>14.113452191</v>
+        <v>14.0915105765</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.306912460651469</v>
+        <v>0.3104031971526404</v>
       </c>
       <c r="T44">
-        <v>1.282942701366679</v>
+        <v>1.300093988997298</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>15.44683830939475</v>
+        <v>15.08760951150185</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1909886723770051</v>
+        <v>0.1902362175761581</v>
       </c>
       <c r="C45">
-        <v>50.92542318745566</v>
+        <v>50.59785659650444</v>
       </c>
       <c r="D45">
-        <v>79.34172318745566</v>
+        <v>79.68525659650444</v>
       </c>
       <c r="E45">
-        <v>20.8473</v>
+        <v>21.5184</v>
       </c>
       <c r="F45">
-        <v>28.8573</v>
+        <v>29.5284</v>
       </c>
       <c r="G45">
         <v>0.441</v>
@@ -4971,28 +4971,28 @@
         <v>21.9</v>
       </c>
       <c r="M45">
-        <v>1.45152219</v>
+        <v>1.48527852</v>
       </c>
       <c r="N45">
-        <v>20.44847781</v>
+        <v>20.41472148</v>
       </c>
       <c r="O45">
-        <v>7.1569672335</v>
+        <v>7.145152517999999</v>
       </c>
       <c r="P45">
-        <v>13.2915105765</v>
+        <v>13.269568962</v>
       </c>
       <c r="Q45">
-        <v>14.0915105765</v>
+        <v>14.069568962</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3104031971526404</v>
+        <v>0.3140186028145679</v>
       </c>
       <c r="T45">
-        <v>1.300093988997298</v>
+        <v>1.317857822614726</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>15.08760951150185</v>
+        <v>14.74470929533135</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1902362175761581</v>
+        <v>0.1894837627753111</v>
       </c>
       <c r="C46">
-        <v>50.59785659650444</v>
+        <v>50.27327780067776</v>
       </c>
       <c r="D46">
-        <v>79.68525659650444</v>
+        <v>80.03177780067776</v>
       </c>
       <c r="E46">
-        <v>21.5184</v>
+        <v>22.1895</v>
       </c>
       <c r="F46">
-        <v>29.5284</v>
+        <v>30.1995</v>
       </c>
       <c r="G46">
         <v>0.441</v>
@@ -5053,28 +5053,28 @@
         <v>21.9</v>
       </c>
       <c r="M46">
-        <v>1.48527852</v>
+        <v>1.51903485</v>
       </c>
       <c r="N46">
-        <v>20.41472148</v>
+        <v>20.38096515</v>
       </c>
       <c r="O46">
-        <v>7.145152517999999</v>
+        <v>7.133337802499999</v>
       </c>
       <c r="P46">
-        <v>13.269568962</v>
+        <v>13.2476273475</v>
       </c>
       <c r="Q46">
-        <v>14.069568962</v>
+        <v>14.0476273475</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3140186028145679</v>
+        <v>0.3177654777732928</v>
       </c>
       <c r="T46">
-        <v>1.317857822614726</v>
+        <v>1.336267613818241</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>14.74470929533135</v>
+        <v>14.41704908876844</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1894837627753111</v>
+        <v>0.1887313079744641</v>
       </c>
       <c r="C47">
-        <v>50.27327780067776</v>
+        <v>49.95172594860931</v>
       </c>
       <c r="D47">
-        <v>80.03177780067776</v>
+        <v>80.3813259486093</v>
       </c>
       <c r="E47">
-        <v>22.1895</v>
+        <v>22.8606</v>
       </c>
       <c r="F47">
-        <v>30.1995</v>
+        <v>30.8706</v>
       </c>
       <c r="G47">
         <v>0.441</v>
@@ -5135,28 +5135,28 @@
         <v>21.9</v>
       </c>
       <c r="M47">
-        <v>1.51903485</v>
+        <v>1.55279118</v>
       </c>
       <c r="N47">
-        <v>20.38096515</v>
+        <v>20.34720882</v>
       </c>
       <c r="O47">
-        <v>7.133337802499999</v>
+        <v>7.121523086999999</v>
       </c>
       <c r="P47">
-        <v>13.2476273475</v>
+        <v>13.225685733</v>
       </c>
       <c r="Q47">
-        <v>14.0476273475</v>
+        <v>14.025685733</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3177654777732928</v>
+        <v>0.3216511258786372</v>
       </c>
       <c r="T47">
-        <v>1.336267613818241</v>
+        <v>1.355359249140405</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>14.41704908876844</v>
+        <v>14.10363497814304</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1887313079744641</v>
+        <v>0.1879788531736171</v>
       </c>
       <c r="C48">
-        <v>49.95172594860931</v>
+        <v>49.63324087587809</v>
       </c>
       <c r="D48">
-        <v>80.3813259486093</v>
+        <v>80.73394087587809</v>
       </c>
       <c r="E48">
-        <v>22.8606</v>
+        <v>23.5317</v>
       </c>
       <c r="F48">
-        <v>30.8706</v>
+        <v>31.5417</v>
       </c>
       <c r="G48">
         <v>0.441</v>
@@ -5217,28 +5217,28 @@
         <v>21.9</v>
       </c>
       <c r="M48">
-        <v>1.55279118</v>
+        <v>1.58654751</v>
       </c>
       <c r="N48">
-        <v>20.34720882</v>
+        <v>20.31345249</v>
       </c>
       <c r="O48">
-        <v>7.121523086999999</v>
+        <v>7.109708371499999</v>
       </c>
       <c r="P48">
-        <v>13.225685733</v>
+        <v>13.2037441185</v>
       </c>
       <c r="Q48">
-        <v>14.025685733</v>
+        <v>14.0037441185</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3216511258786372</v>
+        <v>0.3256834022143719</v>
       </c>
       <c r="T48">
-        <v>1.355359249140405</v>
+        <v>1.37517132353133</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>14.10363497814304</v>
+        <v>13.80355763818255</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1879788531736171</v>
+        <v>0.1872263983727701</v>
       </c>
       <c r="C49">
-        <v>49.63324087587809</v>
+        <v>49.31786312014215</v>
       </c>
       <c r="D49">
-        <v>80.73394087587809</v>
+        <v>81.08966312014215</v>
       </c>
       <c r="E49">
-        <v>23.5317</v>
+        <v>24.2028</v>
       </c>
       <c r="F49">
-        <v>31.5417</v>
+        <v>32.2128</v>
       </c>
       <c r="G49">
         <v>0.441</v>
@@ -5299,28 +5299,28 @@
         <v>21.9</v>
       </c>
       <c r="M49">
-        <v>1.58654751</v>
+        <v>1.62030384</v>
       </c>
       <c r="N49">
-        <v>20.31345249</v>
+        <v>20.27969616</v>
       </c>
       <c r="O49">
-        <v>7.109708371499999</v>
+        <v>7.097893655999999</v>
       </c>
       <c r="P49">
-        <v>13.2037441185</v>
+        <v>13.181802504</v>
       </c>
       <c r="Q49">
-        <v>14.0037441185</v>
+        <v>13.981802504</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3256834022143719</v>
+        <v>0.329870766101481</v>
       </c>
       <c r="T49">
-        <v>1.37517132353133</v>
+        <v>1.395745400783445</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>13.80355763818255</v>
+        <v>13.51598352072041</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1872263983727701</v>
+        <v>0.1864739435719231</v>
       </c>
       <c r="C50">
-        <v>49.31786312014215</v>
+        <v>49.00563393667416</v>
       </c>
       <c r="D50">
-        <v>81.08966312014215</v>
+        <v>81.44853393667415</v>
       </c>
       <c r="E50">
-        <v>24.2028</v>
+        <v>24.8739</v>
       </c>
       <c r="F50">
-        <v>32.2128</v>
+        <v>32.8839</v>
       </c>
       <c r="G50">
         <v>0.441</v>
@@ -5381,28 +5381,28 @@
         <v>21.9</v>
       </c>
       <c r="M50">
-        <v>1.62030384</v>
+        <v>1.65406017</v>
       </c>
       <c r="N50">
-        <v>20.27969616</v>
+        <v>20.24593983</v>
       </c>
       <c r="O50">
-        <v>7.097893655999999</v>
+        <v>7.086078940499998</v>
       </c>
       <c r="P50">
-        <v>13.181802504</v>
+        <v>13.1598608895</v>
       </c>
       <c r="Q50">
-        <v>13.981802504</v>
+        <v>13.9598608895</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.329870766101481</v>
+        <v>0.3342223403371041</v>
       </c>
       <c r="T50">
-        <v>1.395745400783445</v>
+        <v>1.417126304594466</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>13.51598352072041</v>
+        <v>13.24014712233836</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1864739435719231</v>
+        <v>0.1857214887710761</v>
       </c>
       <c r="C51">
-        <v>49.00563393667416</v>
+        <v>48.69659531431132</v>
       </c>
       <c r="D51">
-        <v>81.44853393667415</v>
+        <v>81.81059531431131</v>
       </c>
       <c r="E51">
-        <v>24.8739</v>
+        <v>25.545</v>
       </c>
       <c r="F51">
-        <v>32.8839</v>
+        <v>33.555</v>
       </c>
       <c r="G51">
         <v>0.441</v>
@@ -5463,28 +5463,28 @@
         <v>21.9</v>
       </c>
       <c r="M51">
-        <v>1.65406017</v>
+        <v>1.6878165</v>
       </c>
       <c r="N51">
-        <v>20.24593983</v>
+        <v>20.2121835</v>
       </c>
       <c r="O51">
-        <v>7.086078940499998</v>
+        <v>7.074264224999999</v>
       </c>
       <c r="P51">
-        <v>13.1598608895</v>
+        <v>13.137919275</v>
       </c>
       <c r="Q51">
-        <v>13.9598608895</v>
+        <v>13.937919275</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3342223403371041</v>
+        <v>0.3387479775421522</v>
       </c>
       <c r="T51">
-        <v>1.417126304594466</v>
+        <v>1.439362444557927</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>13.24014712233836</v>
+        <v>12.97534417989159</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1857214887710761</v>
+        <v>0.1854662839702291</v>
       </c>
       <c r="C52">
-        <v>48.69659531431132</v>
+        <v>48.14902523767186</v>
       </c>
       <c r="D52">
-        <v>81.81059531431131</v>
+        <v>81.93412523767186</v>
       </c>
       <c r="E52">
-        <v>25.545</v>
+        <v>26.2161</v>
       </c>
       <c r="F52">
-        <v>33.555</v>
+        <v>34.2261</v>
       </c>
       <c r="G52">
         <v>0.441</v>
@@ -5545,45 +5545,45 @@
         <v>21.9</v>
       </c>
       <c r="M52">
-        <v>1.6878165</v>
+        <v>1.77291198</v>
       </c>
       <c r="N52">
-        <v>20.2121835</v>
+        <v>20.12708802</v>
       </c>
       <c r="O52">
-        <v>7.074264224999999</v>
+        <v>7.044480806999999</v>
       </c>
       <c r="P52">
-        <v>13.137919275</v>
+        <v>13.082607213</v>
       </c>
       <c r="Q52">
-        <v>13.937919275</v>
+        <v>13.882607213</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3387479775421522</v>
+        <v>0.3434583346331206</v>
       </c>
       <c r="T52">
-        <v>1.439362444557927</v>
+        <v>1.462506182070918</v>
       </c>
       <c r="U52">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V52">
         <v>0.35</v>
       </c>
       <c r="W52">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y52">
-        <v>12.97534417989159</v>
+        <v>12.35255909320439</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1854662839702291</v>
+        <v>0.1847235791693822</v>
       </c>
       <c r="C53">
-        <v>48.14902523767186</v>
+        <v>47.83955774180934</v>
       </c>
       <c r="D53">
-        <v>81.93412523767186</v>
+        <v>82.29575774180934</v>
       </c>
       <c r="E53">
-        <v>26.2161</v>
+        <v>26.8872</v>
       </c>
       <c r="F53">
-        <v>34.2261</v>
+        <v>34.8972</v>
       </c>
       <c r="G53">
         <v>0.441</v>
@@ -5627,28 +5627,28 @@
         <v>21.9</v>
       </c>
       <c r="M53">
-        <v>1.77291198</v>
+        <v>1.80767496</v>
       </c>
       <c r="N53">
-        <v>20.12708802</v>
+        <v>20.09232504</v>
       </c>
       <c r="O53">
-        <v>7.044480806999999</v>
+        <v>7.032313763999999</v>
       </c>
       <c r="P53">
-        <v>13.082607213</v>
+        <v>13.060011276</v>
       </c>
       <c r="Q53">
-        <v>13.882607213</v>
+        <v>13.860011276</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3434583346331206</v>
+        <v>0.3483649566028795</v>
       </c>
       <c r="T53">
-        <v>1.462506182070918</v>
+        <v>1.486614241980284</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>12.35255909320439</v>
+        <v>12.11500987987354</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1847235791693822</v>
+        <v>0.1839808743685352</v>
       </c>
       <c r="C54">
-        <v>47.83955774180934</v>
+        <v>47.53329667163438</v>
       </c>
       <c r="D54">
-        <v>82.29575774180934</v>
+        <v>82.66059667163438</v>
       </c>
       <c r="E54">
-        <v>26.8872</v>
+        <v>27.5583</v>
       </c>
       <c r="F54">
-        <v>34.8972</v>
+        <v>35.5683</v>
       </c>
       <c r="G54">
         <v>0.441</v>
@@ -5709,28 +5709,28 @@
         <v>21.9</v>
       </c>
       <c r="M54">
-        <v>1.80767496</v>
+        <v>1.84243794</v>
       </c>
       <c r="N54">
-        <v>20.09232504</v>
+        <v>20.05756206</v>
       </c>
       <c r="O54">
-        <v>7.032313763999999</v>
+        <v>7.020146720999999</v>
       </c>
       <c r="P54">
-        <v>13.060011276</v>
+        <v>13.037415339</v>
       </c>
       <c r="Q54">
-        <v>13.860011276</v>
+        <v>13.837415339</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3483649566028795</v>
+        <v>0.3534803709968833</v>
       </c>
       <c r="T54">
-        <v>1.486614241980284</v>
+        <v>1.511748176779409</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>12.11500987987354</v>
+        <v>11.88642478780045</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1839808743685352</v>
+        <v>0.1832381695676882</v>
       </c>
       <c r="C55">
-        <v>47.53329667163438</v>
+        <v>47.2302848618521</v>
       </c>
       <c r="D55">
-        <v>82.66059667163438</v>
+        <v>83.0286848618521</v>
       </c>
       <c r="E55">
-        <v>27.5583</v>
+        <v>28.22940000000001</v>
       </c>
       <c r="F55">
-        <v>35.5683</v>
+        <v>36.2394</v>
       </c>
       <c r="G55">
         <v>0.441</v>
@@ -5791,28 +5791,28 @@
         <v>21.9</v>
       </c>
       <c r="M55">
-        <v>1.84243794</v>
+        <v>1.87720092</v>
       </c>
       <c r="N55">
-        <v>20.05756206</v>
+        <v>20.02279908</v>
       </c>
       <c r="O55">
-        <v>7.020146720999999</v>
+        <v>7.007979677999999</v>
       </c>
       <c r="P55">
-        <v>13.037415339</v>
+        <v>13.014819402</v>
       </c>
       <c r="Q55">
-        <v>13.837415339</v>
+        <v>13.814819402</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3534803709968833</v>
+        <v>0.3588181947123656</v>
       </c>
       <c r="T55">
-        <v>1.511748176779409</v>
+        <v>1.53797489135241</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>11.88642478780045</v>
+        <v>11.66630581024859</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1832381695676882</v>
+        <v>0.1824954647668412</v>
       </c>
       <c r="C56">
-        <v>47.2302848618521</v>
+        <v>46.93056591355327</v>
       </c>
       <c r="D56">
-        <v>83.0286848618521</v>
+        <v>83.40006591355328</v>
       </c>
       <c r="E56">
-        <v>28.22940000000001</v>
+        <v>28.90050000000001</v>
       </c>
       <c r="F56">
-        <v>36.2394</v>
+        <v>36.91050000000001</v>
       </c>
       <c r="G56">
         <v>0.441</v>
@@ -5873,28 +5873,28 @@
         <v>21.9</v>
       </c>
       <c r="M56">
-        <v>1.87720092</v>
+        <v>1.9119639</v>
       </c>
       <c r="N56">
-        <v>20.02279908</v>
+        <v>19.9880361</v>
       </c>
       <c r="O56">
-        <v>7.007979677999999</v>
+        <v>6.995812634999999</v>
       </c>
       <c r="P56">
-        <v>13.014819402</v>
+        <v>12.992223465</v>
       </c>
       <c r="Q56">
-        <v>13.814819402</v>
+        <v>13.792223465</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3588181947123656</v>
+        <v>0.3643932550374249</v>
       </c>
       <c r="T56">
-        <v>1.53797489135241</v>
+        <v>1.565367237684211</v>
       </c>
       <c r="U56">
         <v>0.0518</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>11.66630581024859</v>
+        <v>11.45419115915316</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1824954647668412</v>
+        <v>0.1817527599659942</v>
       </c>
       <c r="C57">
-        <v>46.93056591355327</v>
+        <v>46.63418421143125</v>
       </c>
       <c r="D57">
-        <v>83.40006591355328</v>
+        <v>83.77478421143125</v>
       </c>
       <c r="E57">
-        <v>28.90050000000001</v>
+        <v>29.5716</v>
       </c>
       <c r="F57">
-        <v>36.91050000000001</v>
+        <v>37.5816</v>
       </c>
       <c r="G57">
         <v>0.441</v>
@@ -5955,28 +5955,28 @@
         <v>21.9</v>
       </c>
       <c r="M57">
-        <v>1.9119639</v>
+        <v>1.94672688</v>
       </c>
       <c r="N57">
-        <v>19.9880361</v>
+        <v>19.95327312</v>
       </c>
       <c r="O57">
-        <v>6.995812634999999</v>
+        <v>6.983645591999999</v>
       </c>
       <c r="P57">
-        <v>12.992223465</v>
+        <v>12.969627528</v>
       </c>
       <c r="Q57">
-        <v>13.792223465</v>
+        <v>13.769627528</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3643932550374249</v>
+        <v>0.3702217271954413</v>
       </c>
       <c r="T57">
-        <v>1.565367237684211</v>
+        <v>1.594004690667457</v>
       </c>
       <c r="U57">
         <v>0.0518</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>11.45419115915316</v>
+        <v>11.24965203131114</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1817527599659942</v>
+        <v>0.1810100551651472</v>
       </c>
       <c r="C58">
-        <v>46.63418421143125</v>
+        <v>46.34118494146512</v>
       </c>
       <c r="D58">
-        <v>83.77478421143125</v>
+        <v>84.15288494146512</v>
       </c>
       <c r="E58">
-        <v>29.5716</v>
+        <v>30.24270000000001</v>
       </c>
       <c r="F58">
-        <v>37.5816</v>
+        <v>38.2527</v>
       </c>
       <c r="G58">
         <v>0.441</v>
@@ -6037,28 +6037,28 @@
         <v>21.9</v>
       </c>
       <c r="M58">
-        <v>1.94672688</v>
+        <v>1.98148986</v>
       </c>
       <c r="N58">
-        <v>19.95327312</v>
+        <v>19.91851014</v>
       </c>
       <c r="O58">
-        <v>6.983645591999999</v>
+        <v>6.971478549</v>
       </c>
       <c r="P58">
-        <v>12.969627528</v>
+        <v>12.947031591</v>
       </c>
       <c r="Q58">
-        <v>13.769627528</v>
+        <v>13.747031591</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3702217271954413</v>
+        <v>0.3763212910817377</v>
       </c>
       <c r="T58">
-        <v>1.594004690667457</v>
+        <v>1.623974118208063</v>
       </c>
       <c r="U58">
         <v>0.0518</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>11.24965203131114</v>
+        <v>11.05228971497235</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1810100551651472</v>
+        <v>0.1802673503643002</v>
       </c>
       <c r="C59">
-        <v>46.34118494146512</v>
+        <v>46.05161410908386</v>
       </c>
       <c r="D59">
-        <v>84.15288494146512</v>
+        <v>84.53441410908387</v>
       </c>
       <c r="E59">
-        <v>30.24270000000001</v>
+        <v>30.91380000000001</v>
       </c>
       <c r="F59">
-        <v>38.2527</v>
+        <v>38.92380000000001</v>
       </c>
       <c r="G59">
         <v>0.441</v>
@@ -6119,28 +6119,28 @@
         <v>21.9</v>
       </c>
       <c r="M59">
-        <v>1.98148986</v>
+        <v>2.01625284</v>
       </c>
       <c r="N59">
-        <v>19.91851014</v>
+        <v>19.88374716</v>
       </c>
       <c r="O59">
-        <v>6.971478549</v>
+        <v>6.959311505999999</v>
       </c>
       <c r="P59">
-        <v>12.947031591</v>
+        <v>12.924435654</v>
       </c>
       <c r="Q59">
-        <v>13.747031591</v>
+        <v>13.724435654</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3763212910817377</v>
+        <v>0.3827113103911911</v>
       </c>
       <c r="T59">
-        <v>1.623974118208063</v>
+        <v>1.655370661345842</v>
       </c>
       <c r="U59">
         <v>0.0518</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>11.05228971497235</v>
+        <v>10.86173299574869</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1802673503643002</v>
+        <v>0.1795246455634532</v>
       </c>
       <c r="C60">
-        <v>46.05161410908387</v>
+        <v>45.76551855782706</v>
       </c>
       <c r="D60">
-        <v>84.53441410908387</v>
+        <v>84.91941855782706</v>
       </c>
       <c r="E60">
-        <v>30.9138</v>
+        <v>31.5849</v>
       </c>
       <c r="F60">
-        <v>38.9238</v>
+        <v>39.5949</v>
       </c>
       <c r="G60">
         <v>0.441</v>
@@ -6201,28 +6201,28 @@
         <v>21.9</v>
       </c>
       <c r="M60">
-        <v>2.01625284</v>
+        <v>2.05101582</v>
       </c>
       <c r="N60">
-        <v>19.88374716</v>
+        <v>19.84898418</v>
       </c>
       <c r="O60">
-        <v>6.959311505999999</v>
+        <v>6.947144462999999</v>
       </c>
       <c r="P60">
-        <v>12.924435654</v>
+        <v>12.901839717</v>
       </c>
       <c r="Q60">
-        <v>13.724435654</v>
+        <v>13.701839717</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3827113103911909</v>
+        <v>0.3894130379596419</v>
       </c>
       <c r="T60">
-        <v>1.655370661345841</v>
+        <v>1.688298743173267</v>
       </c>
       <c r="U60">
         <v>0.0518</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>10.86173299574869</v>
+        <v>10.67763582632922</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1795246455634532</v>
+        <v>0.1787819407626062</v>
       </c>
       <c r="C61">
-        <v>45.76551855782706</v>
+        <v>45.48294598851749</v>
       </c>
       <c r="D61">
-        <v>84.91941855782706</v>
+        <v>85.30794598851749</v>
       </c>
       <c r="E61">
-        <v>31.5849</v>
+        <v>32.256</v>
       </c>
       <c r="F61">
-        <v>39.5949</v>
+        <v>40.266</v>
       </c>
       <c r="G61">
         <v>0.441</v>
@@ -6283,28 +6283,28 @@
         <v>21.9</v>
       </c>
       <c r="M61">
-        <v>2.05101582</v>
+        <v>2.0857788</v>
       </c>
       <c r="N61">
-        <v>19.84898418</v>
+        <v>19.8142212</v>
       </c>
       <c r="O61">
-        <v>6.947144462999999</v>
+        <v>6.934977419999999</v>
       </c>
       <c r="P61">
-        <v>12.901839717</v>
+        <v>12.87924378</v>
       </c>
       <c r="Q61">
-        <v>13.701839717</v>
+        <v>13.67924378</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3894130379596419</v>
+        <v>0.3964498519065155</v>
       </c>
       <c r="T61">
-        <v>1.688298743173267</v>
+        <v>1.722873229092064</v>
       </c>
       <c r="U61">
         <v>0.0518</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>10.67763582632922</v>
+        <v>10.49967522922373</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1787819407626062</v>
+        <v>0.1780392359617592</v>
       </c>
       <c r="C62">
-        <v>45.48294598851749</v>
+        <v>45.20394497896284</v>
       </c>
       <c r="D62">
-        <v>85.30794598851749</v>
+        <v>85.70004497896284</v>
       </c>
       <c r="E62">
-        <v>32.256</v>
+        <v>32.9271</v>
       </c>
       <c r="F62">
-        <v>40.266</v>
+        <v>40.9371</v>
       </c>
       <c r="G62">
         <v>0.441</v>
@@ -6365,28 +6365,28 @@
         <v>21.9</v>
       </c>
       <c r="M62">
-        <v>2.0857788</v>
+        <v>2.12054178</v>
       </c>
       <c r="N62">
-        <v>19.8142212</v>
+        <v>19.77945822</v>
       </c>
       <c r="O62">
-        <v>6.934977419999999</v>
+        <v>6.922810376999999</v>
       </c>
       <c r="P62">
-        <v>12.87924378</v>
+        <v>12.856647843</v>
       </c>
       <c r="Q62">
-        <v>13.67924378</v>
+        <v>13.656647843</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3964498519065155</v>
+        <v>0.403847528107075</v>
       </c>
       <c r="T62">
-        <v>1.722873229092064</v>
+        <v>1.7592207655708</v>
       </c>
       <c r="U62">
         <v>0.0518</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>10.49967522922373</v>
+        <v>10.32754940579383</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1780392359617592</v>
+        <v>0.1772965311609123</v>
       </c>
       <c r="C63">
-        <v>45.20394497896284</v>
+        <v>44.92856500420307</v>
       </c>
       <c r="D63">
-        <v>85.70004497896284</v>
+        <v>86.09576500420306</v>
       </c>
       <c r="E63">
-        <v>32.9271</v>
+        <v>33.5982</v>
       </c>
       <c r="F63">
-        <v>40.9371</v>
+        <v>41.6082</v>
       </c>
       <c r="G63">
         <v>0.441</v>
@@ -6447,28 +6447,28 @@
         <v>21.9</v>
       </c>
       <c r="M63">
-        <v>2.12054178</v>
+        <v>2.15530476</v>
       </c>
       <c r="N63">
-        <v>19.77945822</v>
+        <v>19.74469524</v>
       </c>
       <c r="O63">
-        <v>6.922810376999999</v>
+        <v>6.910643334</v>
       </c>
       <c r="P63">
-        <v>12.856647843</v>
+        <v>12.834051906</v>
       </c>
       <c r="Q63">
-        <v>13.656647843</v>
+        <v>13.634051906</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.403847528107075</v>
+        <v>0.4116345556866112</v>
       </c>
       <c r="T63">
-        <v>1.7592207655708</v>
+        <v>1.797481330285259</v>
       </c>
       <c r="U63">
         <v>0.0518</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>10.32754940579383</v>
+        <v>10.16097602828103</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1772965311609123</v>
+        <v>0.1765538263600652</v>
       </c>
       <c r="C64">
-        <v>44.92856500420307</v>
+        <v>44.65685645732136</v>
       </c>
       <c r="D64">
-        <v>86.09576500420306</v>
+        <v>86.49515645732136</v>
       </c>
       <c r="E64">
-        <v>33.5982</v>
+        <v>34.2693</v>
       </c>
       <c r="F64">
-        <v>41.6082</v>
+        <v>42.2793</v>
       </c>
       <c r="G64">
         <v>0.441</v>
@@ -6529,28 +6529,28 @@
         <v>21.9</v>
       </c>
       <c r="M64">
-        <v>2.15530476</v>
+        <v>2.19006774</v>
       </c>
       <c r="N64">
-        <v>19.74469524</v>
+        <v>19.70993226</v>
       </c>
       <c r="O64">
-        <v>6.910643334</v>
+        <v>6.898476290999999</v>
       </c>
       <c r="P64">
-        <v>12.834051906</v>
+        <v>12.811455969</v>
       </c>
       <c r="Q64">
-        <v>13.634051906</v>
+        <v>13.611455969</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4116345556866112</v>
+        <v>0.419842503675852</v>
       </c>
       <c r="T64">
-        <v>1.797481330285259</v>
+        <v>1.837810033632931</v>
       </c>
       <c r="U64">
         <v>0.0518</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>10.16097602828103</v>
+        <v>9.999690694498792</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1765538263600652</v>
+        <v>0.1758111215592183</v>
       </c>
       <c r="C65">
-        <v>44.65685645732136</v>
+        <v>44.38887067083688</v>
       </c>
       <c r="D65">
-        <v>86.49515645732136</v>
+        <v>86.89827067083688</v>
       </c>
       <c r="E65">
-        <v>34.2693</v>
+        <v>34.9404</v>
       </c>
       <c r="F65">
-        <v>42.2793</v>
+        <v>42.9504</v>
       </c>
       <c r="G65">
         <v>0.441</v>
@@ -6611,28 +6611,28 @@
         <v>21.9</v>
       </c>
       <c r="M65">
-        <v>2.19006774</v>
+        <v>2.22483072</v>
       </c>
       <c r="N65">
-        <v>19.70993226</v>
+        <v>19.67516928</v>
       </c>
       <c r="O65">
-        <v>6.898476290999999</v>
+        <v>6.886309247999999</v>
       </c>
       <c r="P65">
-        <v>12.811455969</v>
+        <v>12.788860032</v>
       </c>
       <c r="Q65">
-        <v>13.611455969</v>
+        <v>13.588860032</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.419842503675852</v>
+        <v>0.4285064487756064</v>
       </c>
       <c r="T65">
-        <v>1.837810033632931</v>
+        <v>1.880379220499919</v>
       </c>
       <c r="U65">
         <v>0.0518</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>9.999690694498792</v>
+        <v>9.843445527397249</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1758111215592183</v>
+        <v>0.1757866667583713</v>
       </c>
       <c r="C66">
-        <v>44.38887067083688</v>
+        <v>43.73110778921771</v>
       </c>
       <c r="D66">
-        <v>86.89827067083688</v>
+        <v>86.91160778921771</v>
       </c>
       <c r="E66">
-        <v>34.9404</v>
+        <v>35.61150000000001</v>
       </c>
       <c r="F66">
-        <v>42.9504</v>
+        <v>43.6215</v>
       </c>
       <c r="G66">
         <v>0.441</v>
@@ -6693,45 +6693,45 @@
         <v>21.9</v>
       </c>
       <c r="M66">
-        <v>2.22483072</v>
+        <v>2.33375025</v>
       </c>
       <c r="N66">
-        <v>19.67516928</v>
+        <v>19.56624975</v>
       </c>
       <c r="O66">
-        <v>6.886309247999999</v>
+        <v>6.848187412499999</v>
       </c>
       <c r="P66">
-        <v>12.788860032</v>
+        <v>12.7180623375</v>
       </c>
       <c r="Q66">
-        <v>13.588860032</v>
+        <v>13.5180623375</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4285064487756064</v>
+        <v>0.4376654764524894</v>
       </c>
       <c r="T66">
-        <v>1.880379220499919</v>
+        <v>1.925380932330734</v>
       </c>
       <c r="U66">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V66">
         <v>0.35</v>
       </c>
       <c r="W66">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>9.843445527397249</v>
+        <v>9.384037559288959</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1757866667583713</v>
+        <v>0.1750550119575243</v>
       </c>
       <c r="C67">
-        <v>43.73110778921771</v>
+        <v>43.46093874062229</v>
       </c>
       <c r="D67">
-        <v>86.91160778921771</v>
+        <v>87.31253874062229</v>
       </c>
       <c r="E67">
-        <v>35.61150000000001</v>
+        <v>36.2826</v>
       </c>
       <c r="F67">
-        <v>43.6215</v>
+        <v>44.2926</v>
       </c>
       <c r="G67">
         <v>0.441</v>
@@ -6775,28 +6775,28 @@
         <v>21.9</v>
       </c>
       <c r="M67">
-        <v>2.33375025</v>
+        <v>2.3696541</v>
       </c>
       <c r="N67">
-        <v>19.56624975</v>
+        <v>19.5303459</v>
       </c>
       <c r="O67">
-        <v>6.848187412499999</v>
+        <v>6.835621065</v>
       </c>
       <c r="P67">
-        <v>12.7180623375</v>
+        <v>12.694724835</v>
       </c>
       <c r="Q67">
-        <v>13.5180623375</v>
+        <v>13.494724835</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.4376654764524894</v>
+        <v>0.4473632704633067</v>
       </c>
       <c r="T67">
-        <v>1.925380932330734</v>
+        <v>1.973029803681009</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>9.384037559288959</v>
+        <v>9.241855172027007</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1750550119575243</v>
+        <v>0.1743233571566773</v>
       </c>
       <c r="C68">
-        <v>43.46093874062229</v>
+        <v>43.19448589524404</v>
       </c>
       <c r="D68">
-        <v>87.31253874062229</v>
+        <v>87.71718589524404</v>
       </c>
       <c r="E68">
-        <v>36.2826</v>
+        <v>36.9537</v>
       </c>
       <c r="F68">
-        <v>44.2926</v>
+        <v>44.9637</v>
       </c>
       <c r="G68">
         <v>0.441</v>
@@ -6857,28 +6857,28 @@
         <v>21.9</v>
       </c>
       <c r="M68">
-        <v>2.3696541</v>
+        <v>2.40555795</v>
       </c>
       <c r="N68">
-        <v>19.5303459</v>
+        <v>19.49444205</v>
       </c>
       <c r="O68">
-        <v>6.835621065</v>
+        <v>6.8230547175</v>
       </c>
       <c r="P68">
-        <v>12.694724835</v>
+        <v>12.6713873325</v>
       </c>
       <c r="Q68">
-        <v>13.494724835</v>
+        <v>13.4713873325</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.4473632704633067</v>
+        <v>0.4576488095656889</v>
       </c>
       <c r="T68">
-        <v>1.973029803681009</v>
+        <v>2.02356648541615</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>9.241855172027007</v>
+        <v>9.103917035131081</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1743233571566773</v>
+        <v>0.1735917023558303</v>
       </c>
       <c r="C69">
-        <v>43.19448589524404</v>
+        <v>42.93180116152413</v>
       </c>
       <c r="D69">
-        <v>87.71718589524404</v>
+        <v>88.12560116152413</v>
       </c>
       <c r="E69">
-        <v>36.9537</v>
+        <v>37.62480000000001</v>
       </c>
       <c r="F69">
-        <v>44.9637</v>
+        <v>45.63480000000001</v>
       </c>
       <c r="G69">
         <v>0.441</v>
@@ -6939,28 +6939,28 @@
         <v>21.9</v>
       </c>
       <c r="M69">
-        <v>2.40555795</v>
+        <v>2.4414618</v>
       </c>
       <c r="N69">
-        <v>19.49444205</v>
+        <v>19.4585382</v>
       </c>
       <c r="O69">
-        <v>6.8230547175</v>
+        <v>6.81048837</v>
       </c>
       <c r="P69">
-        <v>12.6713873325</v>
+        <v>12.64804983</v>
       </c>
       <c r="Q69">
-        <v>13.4713873325</v>
+        <v>13.44804983</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4576488095656889</v>
+        <v>0.4685771948619698</v>
       </c>
       <c r="T69">
-        <v>2.02356648541615</v>
+        <v>2.077261709759736</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>9.103917035131081</v>
+        <v>8.970035902261504</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1735917023558303</v>
+        <v>0.1728600475549833</v>
       </c>
       <c r="C70">
-        <v>42.93180116152413</v>
+        <v>42.6729374191784</v>
       </c>
       <c r="D70">
-        <v>88.12560116152413</v>
+        <v>88.5378374191784</v>
       </c>
       <c r="E70">
-        <v>37.62480000000001</v>
+        <v>38.2959</v>
       </c>
       <c r="F70">
-        <v>45.63480000000001</v>
+        <v>46.3059</v>
       </c>
       <c r="G70">
         <v>0.441</v>
@@ -7021,28 +7021,28 @@
         <v>21.9</v>
       </c>
       <c r="M70">
-        <v>2.4414618</v>
+        <v>2.47736565</v>
       </c>
       <c r="N70">
-        <v>19.4585382</v>
+        <v>19.42263435</v>
       </c>
       <c r="O70">
-        <v>6.81048837</v>
+        <v>6.797922022499999</v>
       </c>
       <c r="P70">
-        <v>12.64804983</v>
+        <v>12.6247123275</v>
       </c>
       <c r="Q70">
-        <v>13.44804983</v>
+        <v>13.4247123275</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4685771948619698</v>
+        <v>0.4802106372741398</v>
       </c>
       <c r="T70">
-        <v>2.077261709759736</v>
+        <v>2.13442114212549</v>
       </c>
       <c r="U70">
         <v>0.0535</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>8.970035902261504</v>
+        <v>8.840035381938876</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1728600475549833</v>
+        <v>0.1721283927541363</v>
       </c>
       <c r="C71">
-        <v>42.6729374191784</v>
+        <v>42.41794854202138</v>
       </c>
       <c r="D71">
-        <v>88.5378374191784</v>
+        <v>88.95394854202138</v>
       </c>
       <c r="E71">
-        <v>38.2959</v>
+        <v>38.96700000000001</v>
       </c>
       <c r="F71">
-        <v>46.3059</v>
+        <v>46.977</v>
       </c>
       <c r="G71">
         <v>0.441</v>
@@ -7103,28 +7103,28 @@
         <v>21.9</v>
       </c>
       <c r="M71">
-        <v>2.47736565</v>
+        <v>2.5132695</v>
       </c>
       <c r="N71">
-        <v>19.42263435</v>
+        <v>19.3867305</v>
       </c>
       <c r="O71">
-        <v>6.797922022499999</v>
+        <v>6.785355674999999</v>
       </c>
       <c r="P71">
-        <v>12.6247123275</v>
+        <v>12.601374825</v>
       </c>
       <c r="Q71">
-        <v>13.4247123275</v>
+        <v>13.401374825</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4802106372741398</v>
+        <v>0.4926196425137879</v>
       </c>
       <c r="T71">
-        <v>2.13442114212549</v>
+        <v>2.195391203315627</v>
       </c>
       <c r="U71">
         <v>0.0535</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>8.840035381938876</v>
+        <v>8.713749162196891</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1721283927541363</v>
+        <v>0.1713967379532893</v>
       </c>
       <c r="C72">
-        <v>42.41794854202138</v>
+        <v>42.166889421437</v>
       </c>
       <c r="D72">
-        <v>88.95394854202138</v>
+        <v>89.373989421437</v>
       </c>
       <c r="E72">
-        <v>38.96700000000001</v>
+        <v>39.63810000000001</v>
       </c>
       <c r="F72">
-        <v>46.977</v>
+        <v>47.64810000000001</v>
       </c>
       <c r="G72">
         <v>0.441</v>
@@ -7185,28 +7185,28 @@
         <v>21.9</v>
       </c>
       <c r="M72">
-        <v>2.5132695</v>
+        <v>2.54917335</v>
       </c>
       <c r="N72">
-        <v>19.3867305</v>
+        <v>19.35082665</v>
       </c>
       <c r="O72">
-        <v>6.785355674999999</v>
+        <v>6.772789327499999</v>
       </c>
       <c r="P72">
-        <v>12.601374825</v>
+        <v>12.5780373225</v>
       </c>
       <c r="Q72">
-        <v>13.401374825</v>
+        <v>13.3780373225</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4926196425137879</v>
+        <v>0.5058844412182392</v>
       </c>
       <c r="T72">
-        <v>2.195391203315627</v>
+        <v>2.26056609631198</v>
       </c>
       <c r="U72">
         <v>0.0535</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>8.713749162196891</v>
+        <v>8.591020300757497</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1713967379532893</v>
+        <v>0.1706650831524424</v>
       </c>
       <c r="C73">
-        <v>42.16688942143701</v>
+        <v>41.91981599051749</v>
       </c>
       <c r="D73">
-        <v>89.373989421437</v>
+        <v>89.79801599051748</v>
       </c>
       <c r="E73">
-        <v>39.6381</v>
+        <v>40.3092</v>
       </c>
       <c r="F73">
-        <v>47.6481</v>
+        <v>48.3192</v>
       </c>
       <c r="G73">
         <v>0.441</v>
@@ -7267,28 +7267,28 @@
         <v>21.9</v>
       </c>
       <c r="M73">
-        <v>2.54917335</v>
+        <v>2.5850772</v>
       </c>
       <c r="N73">
-        <v>19.35082665</v>
+        <v>19.3149228</v>
       </c>
       <c r="O73">
-        <v>6.772789327499999</v>
+        <v>6.760222979999999</v>
       </c>
       <c r="P73">
-        <v>12.5780373225</v>
+        <v>12.55469982</v>
       </c>
       <c r="Q73">
-        <v>13.3780373225</v>
+        <v>13.35469982</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5058844412182391</v>
+        <v>0.520096725544437</v>
       </c>
       <c r="T73">
-        <v>2.26056609631198</v>
+        <v>2.330396338808073</v>
       </c>
       <c r="U73">
         <v>0.0535</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>8.591020300757499</v>
+        <v>8.471700574358088</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1706650831524424</v>
+        <v>0.1699334283515954</v>
       </c>
       <c r="C74">
-        <v>41.91981599051749</v>
+        <v>41.67678524889249</v>
       </c>
       <c r="D74">
-        <v>89.79801599051748</v>
+        <v>90.22608524889249</v>
       </c>
       <c r="E74">
-        <v>40.3092</v>
+        <v>40.9803</v>
       </c>
       <c r="F74">
-        <v>48.3192</v>
+        <v>48.9903</v>
       </c>
       <c r="G74">
         <v>0.441</v>
@@ -7349,28 +7349,28 @@
         <v>21.9</v>
       </c>
       <c r="M74">
-        <v>2.5850772</v>
+        <v>2.62098105</v>
       </c>
       <c r="N74">
-        <v>19.3149228</v>
+        <v>19.27901895</v>
       </c>
       <c r="O74">
-        <v>6.760222979999999</v>
+        <v>6.747656632499999</v>
       </c>
       <c r="P74">
-        <v>12.55469982</v>
+        <v>12.5313623175</v>
       </c>
       <c r="Q74">
-        <v>13.35469982</v>
+        <v>13.3313623175</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.520096725544437</v>
+        <v>0.5353617716725754</v>
       </c>
       <c r="T74">
-        <v>2.330396338808073</v>
+        <v>2.405399191859432</v>
       </c>
       <c r="U74">
         <v>0.0535</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>8.471700574358088</v>
+        <v>8.355649881558662</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1699334283515954</v>
+        <v>0.1692017735507484</v>
       </c>
       <c r="C75">
-        <v>41.67678524889249</v>
+        <v>41.43785528827202</v>
       </c>
       <c r="D75">
-        <v>90.22608524889249</v>
+        <v>90.65825528827202</v>
       </c>
       <c r="E75">
-        <v>40.9803</v>
+        <v>41.6514</v>
       </c>
       <c r="F75">
-        <v>48.9903</v>
+        <v>49.6614</v>
       </c>
       <c r="G75">
         <v>0.441</v>
@@ -7431,28 +7431,28 @@
         <v>21.9</v>
       </c>
       <c r="M75">
-        <v>2.62098105</v>
+        <v>2.6568849</v>
       </c>
       <c r="N75">
-        <v>19.27901895</v>
+        <v>19.2431151</v>
       </c>
       <c r="O75">
-        <v>6.747656632499999</v>
+        <v>6.735090284999998</v>
       </c>
       <c r="P75">
-        <v>12.5313623175</v>
+        <v>12.508024815</v>
       </c>
       <c r="Q75">
-        <v>13.3313623175</v>
+        <v>13.308024815</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.5353617716725754</v>
+        <v>0.5518010521182629</v>
       </c>
       <c r="T75">
-        <v>2.405399191859432</v>
+        <v>2.486171495145511</v>
       </c>
       <c r="U75">
         <v>0.0535</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>8.355649881558662</v>
+        <v>8.242735693970031</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1692017735507484</v>
+        <v>0.1684701187499014</v>
       </c>
       <c r="C76">
-        <v>41.43785528827202</v>
+        <v>41.20308531872665</v>
       </c>
       <c r="D76">
-        <v>90.65825528827202</v>
+        <v>91.09458531872664</v>
       </c>
       <c r="E76">
-        <v>41.6514</v>
+        <v>42.3225</v>
       </c>
       <c r="F76">
-        <v>49.6614</v>
+        <v>50.3325</v>
       </c>
       <c r="G76">
         <v>0.441</v>
@@ -7513,28 +7513,28 @@
         <v>21.9</v>
       </c>
       <c r="M76">
-        <v>2.6568849</v>
+        <v>2.69278875</v>
       </c>
       <c r="N76">
-        <v>19.2431151</v>
+        <v>19.20721125</v>
       </c>
       <c r="O76">
-        <v>6.735090284999998</v>
+        <v>6.7225239375</v>
       </c>
       <c r="P76">
-        <v>12.508024815</v>
+        <v>12.4846873125</v>
       </c>
       <c r="Q76">
-        <v>13.308024815</v>
+        <v>13.2846873125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.5518010521182629</v>
+        <v>0.5695554749996056</v>
       </c>
       <c r="T76">
-        <v>2.486171495145511</v>
+        <v>2.573405582694476</v>
       </c>
       <c r="U76">
         <v>0.0535</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>8.242735693970031</v>
+        <v>8.132832551383768</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1684701187499014</v>
+        <v>0.1677384639490544</v>
       </c>
       <c r="C77">
-        <v>41.20308531872665</v>
+        <v>40.97253569573083</v>
       </c>
       <c r="D77">
-        <v>91.09458531872664</v>
+        <v>91.53513569573083</v>
       </c>
       <c r="E77">
-        <v>42.3225</v>
+        <v>42.9936</v>
       </c>
       <c r="F77">
-        <v>50.3325</v>
+        <v>51.0036</v>
       </c>
       <c r="G77">
         <v>0.441</v>
@@ -7595,28 +7595,28 @@
         <v>21.9</v>
       </c>
       <c r="M77">
-        <v>2.69278875</v>
+        <v>2.7286926</v>
       </c>
       <c r="N77">
-        <v>19.20721125</v>
+        <v>19.1713074</v>
       </c>
       <c r="O77">
-        <v>6.7225239375</v>
+        <v>6.709957589999999</v>
       </c>
       <c r="P77">
-        <v>12.4846873125</v>
+        <v>12.46134981</v>
       </c>
       <c r="Q77">
-        <v>13.2846873125</v>
+        <v>13.26134981</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.5695554749996056</v>
+        <v>0.5887894331210599</v>
       </c>
       <c r="T77">
-        <v>2.573405582694476</v>
+        <v>2.667909177539189</v>
       </c>
       <c r="U77">
         <v>0.0535</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>8.132832551383768</v>
+        <v>8.025821596760295</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1677384639490544</v>
+        <v>0.1670068091482074</v>
       </c>
       <c r="C78">
-        <v>40.97253569573083</v>
+        <v>40.74626794799418</v>
       </c>
       <c r="D78">
-        <v>91.53513569573083</v>
+        <v>91.97996794799418</v>
       </c>
       <c r="E78">
-        <v>42.9936</v>
+        <v>43.6647</v>
       </c>
       <c r="F78">
-        <v>51.0036</v>
+        <v>51.6747</v>
       </c>
       <c r="G78">
         <v>0.441</v>
@@ -7677,28 +7677,28 @@
         <v>21.9</v>
       </c>
       <c r="M78">
-        <v>2.7286926</v>
+        <v>2.76459645</v>
       </c>
       <c r="N78">
-        <v>19.1713074</v>
+        <v>19.13540355</v>
       </c>
       <c r="O78">
-        <v>6.709957589999999</v>
+        <v>6.697391242499999</v>
       </c>
       <c r="P78">
-        <v>12.46134981</v>
+        <v>12.4380123075</v>
       </c>
       <c r="Q78">
-        <v>13.26134981</v>
+        <v>13.2380123075</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5887894331210599</v>
+        <v>0.6096959093400321</v>
       </c>
       <c r="T78">
-        <v>2.667909177539189</v>
+        <v>2.770630476283441</v>
       </c>
       <c r="U78">
         <v>0.0535</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>8.025821596760295</v>
+        <v>7.921590147451719</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1670068091482074</v>
+        <v>0.1662751543473604</v>
       </c>
       <c r="C79">
-        <v>40.74626794799418</v>
+        <v>40.52434480610845</v>
       </c>
       <c r="D79">
-        <v>91.97996794799418</v>
+        <v>92.42914480610845</v>
       </c>
       <c r="E79">
-        <v>43.6647</v>
+        <v>44.33580000000001</v>
       </c>
       <c r="F79">
-        <v>51.6747</v>
+        <v>52.3458</v>
       </c>
       <c r="G79">
         <v>0.441</v>
@@ -7759,28 +7759,28 @@
         <v>21.9</v>
       </c>
       <c r="M79">
-        <v>2.76459645</v>
+        <v>2.8005003</v>
       </c>
       <c r="N79">
-        <v>19.13540355</v>
+        <v>19.0994997</v>
       </c>
       <c r="O79">
-        <v>6.697391242499999</v>
+        <v>6.684824894999999</v>
       </c>
       <c r="P79">
-        <v>12.4380123075</v>
+        <v>12.414674805</v>
       </c>
       <c r="Q79">
-        <v>13.2380123075</v>
+        <v>13.214674805</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.6096959093400321</v>
+        <v>0.6325029743061836</v>
       </c>
       <c r="T79">
-        <v>2.770630476283441</v>
+        <v>2.882690074913535</v>
       </c>
       <c r="U79">
         <v>0.0535</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>7.921590147451719</v>
+        <v>7.820031299407466</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1662751543473604</v>
+        <v>0.1655434995465134</v>
       </c>
       <c r="C80">
-        <v>40.52434480610845</v>
+        <v>40.30683023203829</v>
       </c>
       <c r="D80">
-        <v>92.42914480610845</v>
+        <v>92.88273023203828</v>
       </c>
       <c r="E80">
-        <v>44.33580000000001</v>
+        <v>45.0069</v>
       </c>
       <c r="F80">
-        <v>52.3458</v>
+        <v>53.0169</v>
       </c>
       <c r="G80">
         <v>0.441</v>
@@ -7841,28 +7841,28 @@
         <v>21.9</v>
       </c>
       <c r="M80">
-        <v>2.8005003</v>
+        <v>2.83640415</v>
       </c>
       <c r="N80">
-        <v>19.0994997</v>
+        <v>19.06359585</v>
       </c>
       <c r="O80">
-        <v>6.684824894999999</v>
+        <v>6.672258547499999</v>
       </c>
       <c r="P80">
-        <v>12.414674805</v>
+        <v>12.3913373025</v>
       </c>
       <c r="Q80">
-        <v>13.214674805</v>
+        <v>13.1913373025</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.6325029743061836</v>
+        <v>0.657482140697683</v>
       </c>
       <c r="T80">
-        <v>2.882690074913535</v>
+        <v>3.005422016270304</v>
       </c>
       <c r="U80">
         <v>0.0535</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>7.820031299407466</v>
+        <v>7.721043561440283</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1655434995465134</v>
+        <v>0.1648118447456664</v>
       </c>
       <c r="C81">
-        <v>40.30683023203829</v>
+        <v>40.09378944948408</v>
       </c>
       <c r="D81">
-        <v>92.88273023203828</v>
+        <v>93.34078944948408</v>
       </c>
       <c r="E81">
-        <v>45.0069</v>
+        <v>45.678</v>
       </c>
       <c r="F81">
-        <v>53.0169</v>
+        <v>53.688</v>
       </c>
       <c r="G81">
         <v>0.441</v>
@@ -7923,28 +7923,28 @@
         <v>21.9</v>
       </c>
       <c r="M81">
-        <v>2.83640415</v>
+        <v>2.872308</v>
       </c>
       <c r="N81">
-        <v>19.06359585</v>
+        <v>19.027692</v>
       </c>
       <c r="O81">
-        <v>6.672258547499999</v>
+        <v>6.659692199999999</v>
       </c>
       <c r="P81">
-        <v>12.3913373025</v>
+        <v>12.3679998</v>
       </c>
       <c r="Q81">
-        <v>13.1913373025</v>
+        <v>13.1679998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.657482140697683</v>
+        <v>0.6849592237283322</v>
       </c>
       <c r="T81">
-        <v>3.005422016270304</v>
+        <v>3.140427151762751</v>
       </c>
       <c r="U81">
         <v>0.0535</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>7.721043561440283</v>
+        <v>7.624530516922279</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1648118447456664</v>
+        <v>0.1645013899448194</v>
       </c>
       <c r="C82">
-        <v>40.09378944948408</v>
+        <v>39.61842063139007</v>
       </c>
       <c r="D82">
-        <v>93.34078944948408</v>
+        <v>93.53652063139008</v>
       </c>
       <c r="E82">
-        <v>45.678</v>
+        <v>46.34910000000001</v>
       </c>
       <c r="F82">
-        <v>53.688</v>
+        <v>54.35910000000001</v>
       </c>
       <c r="G82">
         <v>0.441</v>
@@ -8005,45 +8005,45 @@
         <v>21.9</v>
       </c>
       <c r="M82">
-        <v>2.872308</v>
+        <v>2.95169913</v>
       </c>
       <c r="N82">
-        <v>19.027692</v>
+        <v>18.94830087</v>
       </c>
       <c r="O82">
-        <v>6.659692199999999</v>
+        <v>6.631905304499998</v>
       </c>
       <c r="P82">
-        <v>12.3679998</v>
+        <v>12.3163955655</v>
       </c>
       <c r="Q82">
-        <v>13.1679998</v>
+        <v>13.1163955655</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6849592237283322</v>
+        <v>0.7153286312885235</v>
       </c>
       <c r="T82">
-        <v>3.140427151762751</v>
+        <v>3.289643354149139</v>
       </c>
       <c r="U82">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V82">
         <v>0.35</v>
       </c>
       <c r="W82">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y82">
-        <v>7.624530516922279</v>
+        <v>7.419455383313406</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1645013899448194</v>
+        <v>0.1637749351439724</v>
       </c>
       <c r="C83">
-        <v>39.61842063139007</v>
+        <v>39.40854922304224</v>
       </c>
       <c r="D83">
-        <v>93.53652063139008</v>
+        <v>93.99774922304223</v>
       </c>
       <c r="E83">
-        <v>46.34910000000001</v>
+        <v>47.0202</v>
       </c>
       <c r="F83">
-        <v>54.35910000000001</v>
+        <v>55.0302</v>
       </c>
       <c r="G83">
         <v>0.441</v>
@@ -8087,28 +8087,28 @@
         <v>21.9</v>
       </c>
       <c r="M83">
-        <v>2.95169913</v>
+        <v>2.98813986</v>
       </c>
       <c r="N83">
-        <v>18.94830087</v>
+        <v>18.91186014</v>
       </c>
       <c r="O83">
-        <v>6.631905304499998</v>
+        <v>6.619151048999999</v>
       </c>
       <c r="P83">
-        <v>12.3163955655</v>
+        <v>12.292709091</v>
       </c>
       <c r="Q83">
-        <v>13.1163955655</v>
+        <v>13.092709091</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.7153286312885235</v>
+        <v>0.7490724174665138</v>
       </c>
       <c r="T83">
-        <v>3.289643354149139</v>
+        <v>3.455439134578459</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>7.419455383313406</v>
+        <v>7.328974220102268</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1637749351439724</v>
+        <v>0.1630484803431255</v>
       </c>
       <c r="C84">
-        <v>39.40854922304224</v>
+        <v>39.2032489916221</v>
       </c>
       <c r="D84">
-        <v>93.99774922304223</v>
+        <v>94.4635489916221</v>
       </c>
       <c r="E84">
-        <v>47.0202</v>
+        <v>47.69130000000001</v>
       </c>
       <c r="F84">
-        <v>55.0302</v>
+        <v>55.7013</v>
       </c>
       <c r="G84">
         <v>0.441</v>
@@ -8169,28 +8169,28 @@
         <v>21.9</v>
       </c>
       <c r="M84">
-        <v>2.98813986</v>
+        <v>3.02458059</v>
       </c>
       <c r="N84">
-        <v>18.91186014</v>
+        <v>18.87541941</v>
       </c>
       <c r="O84">
-        <v>6.619151048999999</v>
+        <v>6.606396793499999</v>
       </c>
       <c r="P84">
-        <v>12.292709091</v>
+        <v>12.2690226165</v>
       </c>
       <c r="Q84">
-        <v>13.092709091</v>
+        <v>13.0690226165</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.7490724174665138</v>
+        <v>0.7867860608419148</v>
       </c>
       <c r="T84">
-        <v>3.455439134578459</v>
+        <v>3.640740300940641</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>7.328974220102268</v>
+        <v>7.240673325884168</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1630484803431255</v>
+        <v>0.1623220255422785</v>
       </c>
       <c r="C85">
-        <v>39.2032489916221</v>
+        <v>39.00258823207604</v>
       </c>
       <c r="D85">
-        <v>94.4635489916221</v>
+        <v>94.93398823207605</v>
       </c>
       <c r="E85">
-        <v>47.69130000000001</v>
+        <v>48.36240000000001</v>
       </c>
       <c r="F85">
-        <v>55.7013</v>
+        <v>56.37240000000001</v>
       </c>
       <c r="G85">
         <v>0.441</v>
@@ -8251,28 +8251,28 @@
         <v>21.9</v>
       </c>
       <c r="M85">
-        <v>3.02458059</v>
+        <v>3.06102132</v>
       </c>
       <c r="N85">
-        <v>18.87541941</v>
+        <v>18.83897868</v>
       </c>
       <c r="O85">
-        <v>6.606396793499999</v>
+        <v>6.593642537999998</v>
       </c>
       <c r="P85">
-        <v>12.2690226165</v>
+        <v>12.245336142</v>
       </c>
       <c r="Q85">
-        <v>13.0690226165</v>
+        <v>13.045336142</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.7867860608419148</v>
+        <v>0.8292139096392408</v>
       </c>
       <c r="T85">
-        <v>3.640740300940641</v>
+        <v>3.849204113098095</v>
       </c>
       <c r="U85">
         <v>0.0543</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>7.240673325884168</v>
+        <v>7.154474833909354</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1623220255422785</v>
+        <v>0.1615955707414315</v>
       </c>
       <c r="C86">
-        <v>39.00258823207602</v>
+        <v>38.80663660662596</v>
       </c>
       <c r="D86">
-        <v>94.93398823207602</v>
+        <v>95.40913660662595</v>
       </c>
       <c r="E86">
-        <v>48.3624</v>
+        <v>49.0335</v>
       </c>
       <c r="F86">
-        <v>56.3724</v>
+        <v>57.04349999999999</v>
       </c>
       <c r="G86">
         <v>0.441</v>
@@ -8333,28 +8333,28 @@
         <v>21.9</v>
       </c>
       <c r="M86">
-        <v>3.06102132</v>
+        <v>3.09746205</v>
       </c>
       <c r="N86">
-        <v>18.83897868</v>
+        <v>18.80253795</v>
       </c>
       <c r="O86">
-        <v>6.593642537999998</v>
+        <v>6.580888282499999</v>
       </c>
       <c r="P86">
-        <v>12.245336142</v>
+        <v>12.2216496675</v>
       </c>
       <c r="Q86">
-        <v>13.045336142</v>
+        <v>13.0216496675</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.8292139096392404</v>
+        <v>0.8772988049428766</v>
       </c>
       <c r="T86">
-        <v>3.849204113098093</v>
+        <v>4.085463100209875</v>
       </c>
       <c r="U86">
         <v>0.0543</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>7.154474833909355</v>
+        <v>7.070304541745717</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1615955707414315</v>
+        <v>0.1608691159405845</v>
       </c>
       <c r="C87">
-        <v>38.80663660662596</v>
+        <v>38.61546517915792</v>
       </c>
       <c r="D87">
-        <v>95.40913660662595</v>
+        <v>95.88906517915791</v>
       </c>
       <c r="E87">
-        <v>49.0335</v>
+        <v>49.7046</v>
       </c>
       <c r="F87">
-        <v>57.04349999999999</v>
+        <v>57.7146</v>
       </c>
       <c r="G87">
         <v>0.441</v>
@@ -8415,28 +8415,28 @@
         <v>21.9</v>
       </c>
       <c r="M87">
-        <v>3.09746205</v>
+        <v>3.13390278</v>
       </c>
       <c r="N87">
-        <v>18.80253795</v>
+        <v>18.76609722</v>
       </c>
       <c r="O87">
-        <v>6.580888282499999</v>
+        <v>6.568134026999999</v>
       </c>
       <c r="P87">
-        <v>12.2216496675</v>
+        <v>12.197963193</v>
       </c>
       <c r="Q87">
-        <v>13.0216496675</v>
+        <v>12.997963193</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.8772988049428766</v>
+        <v>0.932252971004175</v>
       </c>
       <c r="T87">
-        <v>4.085463100209875</v>
+        <v>4.355473371194767</v>
       </c>
       <c r="U87">
         <v>0.0543</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>7.070304541745717</v>
+        <v>6.988091698237046</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1608691159405845</v>
+        <v>0.1601426611397375</v>
       </c>
       <c r="C88">
-        <v>38.61546517915792</v>
+        <v>38.42914645065377</v>
       </c>
       <c r="D88">
-        <v>95.88906517915791</v>
+        <v>96.37384645065377</v>
       </c>
       <c r="E88">
-        <v>49.7046</v>
+        <v>50.3757</v>
       </c>
       <c r="F88">
-        <v>57.7146</v>
+        <v>58.3857</v>
       </c>
       <c r="G88">
         <v>0.441</v>
@@ -8497,28 +8497,28 @@
         <v>21.9</v>
       </c>
       <c r="M88">
-        <v>3.13390278</v>
+        <v>3.17034351</v>
       </c>
       <c r="N88">
-        <v>18.76609722</v>
+        <v>18.72965649</v>
       </c>
       <c r="O88">
-        <v>6.568134026999999</v>
+        <v>6.555379771499999</v>
       </c>
       <c r="P88">
-        <v>12.197963193</v>
+        <v>12.1742767185</v>
       </c>
       <c r="Q88">
-        <v>12.997963193</v>
+        <v>12.9742767185</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.932252971004175</v>
+        <v>0.9956616241518269</v>
       </c>
       <c r="T88">
-        <v>4.355473371194767</v>
+        <v>4.667023683869643</v>
       </c>
       <c r="U88">
         <v>0.0543</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>6.988091698237046</v>
+        <v>6.907768805153862</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1601426611397375</v>
+        <v>0.1594162063388905</v>
       </c>
       <c r="C89">
-        <v>38.42914645065377</v>
+        <v>38.24775439570272</v>
       </c>
       <c r="D89">
-        <v>96.37384645065377</v>
+        <v>96.86355439570272</v>
       </c>
       <c r="E89">
-        <v>50.3757</v>
+        <v>51.0468</v>
       </c>
       <c r="F89">
-        <v>58.3857</v>
+        <v>59.0568</v>
       </c>
       <c r="G89">
         <v>0.441</v>
@@ -8579,28 +8579,28 @@
         <v>21.9</v>
       </c>
       <c r="M89">
-        <v>3.17034351</v>
+        <v>3.20678424</v>
       </c>
       <c r="N89">
-        <v>18.72965649</v>
+        <v>18.69321576</v>
       </c>
       <c r="O89">
-        <v>6.555379771499999</v>
+        <v>6.542625515999998</v>
       </c>
       <c r="P89">
-        <v>12.1742767185</v>
+        <v>12.150590244</v>
       </c>
       <c r="Q89">
-        <v>12.9742767185</v>
+        <v>12.950590244</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.9956616241518269</v>
+        <v>1.069638386157421</v>
       </c>
       <c r="T89">
-        <v>4.667023683869643</v>
+        <v>5.030499048656999</v>
       </c>
       <c r="U89">
         <v>0.0543</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>6.907768805153862</v>
+        <v>6.829271432368022</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1594162063388905</v>
+        <v>0.1586897515380435</v>
       </c>
       <c r="C90">
-        <v>38.24775439570272</v>
+        <v>38.07136450013243</v>
       </c>
       <c r="D90">
-        <v>96.86355439570272</v>
+        <v>97.35826450013242</v>
       </c>
       <c r="E90">
-        <v>51.0468</v>
+        <v>51.7179</v>
       </c>
       <c r="F90">
-        <v>59.0568</v>
+        <v>59.7279</v>
       </c>
       <c r="G90">
         <v>0.441</v>
@@ -8661,28 +8661,28 @@
         <v>21.9</v>
       </c>
       <c r="M90">
-        <v>3.20678424</v>
+        <v>3.24322497</v>
       </c>
       <c r="N90">
-        <v>18.69321576</v>
+        <v>18.65677503</v>
       </c>
       <c r="O90">
-        <v>6.542625515999998</v>
+        <v>6.529871260499999</v>
       </c>
       <c r="P90">
-        <v>12.150590244</v>
+        <v>12.1269037695</v>
       </c>
       <c r="Q90">
-        <v>12.950590244</v>
+        <v>12.9269037695</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.069638386157421</v>
+        <v>1.157065468527669</v>
       </c>
       <c r="T90">
-        <v>5.030499048656999</v>
+        <v>5.460060843405691</v>
       </c>
       <c r="U90">
         <v>0.0543</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>6.829271432368022</v>
+        <v>6.752538045487483</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1586897515380435</v>
+        <v>0.1579632967371965</v>
       </c>
       <c r="C91">
-        <v>38.07136450013243</v>
+        <v>37.90005379979843</v>
       </c>
       <c r="D91">
-        <v>97.35826450013242</v>
+        <v>97.85805379979843</v>
       </c>
       <c r="E91">
-        <v>51.7179</v>
+        <v>52.389</v>
       </c>
       <c r="F91">
-        <v>59.7279</v>
+        <v>60.399</v>
       </c>
       <c r="G91">
         <v>0.441</v>
@@ -8743,28 +8743,28 @@
         <v>21.9</v>
       </c>
       <c r="M91">
-        <v>3.24322497</v>
+        <v>3.2796657</v>
       </c>
       <c r="N91">
-        <v>18.65677503</v>
+        <v>18.6203343</v>
       </c>
       <c r="O91">
-        <v>6.529871260499999</v>
+        <v>6.517117004999999</v>
       </c>
       <c r="P91">
-        <v>12.1269037695</v>
+        <v>12.103217295</v>
       </c>
       <c r="Q91">
-        <v>12.9269037695</v>
+        <v>12.903217295</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.157065468527669</v>
+        <v>1.261977967371966</v>
       </c>
       <c r="T91">
-        <v>5.460060843405691</v>
+        <v>5.975534997104123</v>
       </c>
       <c r="U91">
         <v>0.0543</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>6.752538045487483</v>
+        <v>6.677509844982066</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1579632967371965</v>
+        <v>0.1572368419363495</v>
       </c>
       <c r="C92">
-        <v>37.90005379979843</v>
+        <v>37.7339009205749</v>
       </c>
       <c r="D92">
-        <v>97.85805379979843</v>
+        <v>98.3630009205749</v>
       </c>
       <c r="E92">
-        <v>52.389</v>
+        <v>53.06010000000001</v>
       </c>
       <c r="F92">
-        <v>60.399</v>
+        <v>61.0701</v>
       </c>
       <c r="G92">
         <v>0.441</v>
@@ -8825,28 +8825,28 @@
         <v>21.9</v>
       </c>
       <c r="M92">
-        <v>3.2796657</v>
+        <v>3.31610643</v>
       </c>
       <c r="N92">
-        <v>18.6203343</v>
+        <v>18.58389357</v>
       </c>
       <c r="O92">
-        <v>6.517117004999999</v>
+        <v>6.504362749499998</v>
       </c>
       <c r="P92">
-        <v>12.103217295</v>
+        <v>12.0795308205</v>
       </c>
       <c r="Q92">
-        <v>12.903217295</v>
+        <v>12.8795308205</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.261977967371966</v>
+        <v>1.390204354848329</v>
       </c>
       <c r="T92">
-        <v>5.975534997104123</v>
+        <v>6.60555896273554</v>
       </c>
       <c r="U92">
         <v>0.0543</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>6.677509844982066</v>
+        <v>6.604130615916328</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1572368419363495</v>
+        <v>0.1565103871355026</v>
       </c>
       <c r="C93">
-        <v>37.7339009205749</v>
+        <v>37.57298611959006</v>
       </c>
       <c r="D93">
-        <v>98.3630009205749</v>
+        <v>98.87318611959006</v>
       </c>
       <c r="E93">
-        <v>53.06010000000001</v>
+        <v>53.7312</v>
       </c>
       <c r="F93">
-        <v>61.0701</v>
+        <v>61.7412</v>
       </c>
       <c r="G93">
         <v>0.441</v>
@@ -8907,28 +8907,28 @@
         <v>21.9</v>
       </c>
       <c r="M93">
-        <v>3.31610643</v>
+        <v>3.35254716</v>
       </c>
       <c r="N93">
-        <v>18.58389357</v>
+        <v>18.54745284</v>
       </c>
       <c r="O93">
-        <v>6.504362749499998</v>
+        <v>6.491608493999999</v>
       </c>
       <c r="P93">
-        <v>12.0795308205</v>
+        <v>12.055844346</v>
       </c>
       <c r="Q93">
-        <v>12.8795308205</v>
+        <v>12.855844346</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.390204354848329</v>
+        <v>1.550487339193783</v>
       </c>
       <c r="T93">
-        <v>6.60555896273554</v>
+        <v>7.393088919774812</v>
       </c>
       <c r="U93">
         <v>0.0543</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>6.604130615916328</v>
+        <v>6.532346587482456</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1565103871355026</v>
+        <v>0.1557839323346555</v>
       </c>
       <c r="C94">
-        <v>37.57298611959006</v>
+        <v>37.41739132775109</v>
       </c>
       <c r="D94">
-        <v>98.87318611959006</v>
+        <v>99.38869132775109</v>
       </c>
       <c r="E94">
-        <v>53.7312</v>
+        <v>54.4023</v>
       </c>
       <c r="F94">
-        <v>61.7412</v>
+        <v>62.4123</v>
       </c>
       <c r="G94">
         <v>0.441</v>
@@ -8989,28 +8989,28 @@
         <v>21.9</v>
       </c>
       <c r="M94">
-        <v>3.35254716</v>
+        <v>3.38898789</v>
       </c>
       <c r="N94">
-        <v>18.54745284</v>
+        <v>18.51101211</v>
       </c>
       <c r="O94">
-        <v>6.491608493999999</v>
+        <v>6.478854238499999</v>
       </c>
       <c r="P94">
-        <v>12.055844346</v>
+        <v>12.0321578715</v>
       </c>
       <c r="Q94">
-        <v>12.855844346</v>
+        <v>12.8321578715</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.550487339193783</v>
+        <v>1.756565461923652</v>
       </c>
       <c r="T94">
-        <v>7.393088919774812</v>
+        <v>8.40562743596816</v>
       </c>
       <c r="U94">
         <v>0.0543</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>6.532346587482456</v>
+        <v>6.462106301595548</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1557839323346555</v>
+        <v>0.1550574775338086</v>
       </c>
       <c r="C95">
-        <v>37.41739132775109</v>
+        <v>37.26720019360672</v>
       </c>
       <c r="D95">
-        <v>99.38869132775109</v>
+        <v>99.90960019360672</v>
       </c>
       <c r="E95">
-        <v>54.4023</v>
+        <v>55.07340000000001</v>
       </c>
       <c r="F95">
-        <v>62.4123</v>
+        <v>63.0834</v>
       </c>
       <c r="G95">
         <v>0.441</v>
@@ -9071,28 +9071,28 @@
         <v>21.9</v>
       </c>
       <c r="M95">
-        <v>3.38898789</v>
+        <v>3.42542862</v>
       </c>
       <c r="N95">
-        <v>18.51101211</v>
+        <v>18.47457138</v>
       </c>
       <c r="O95">
-        <v>6.478854238499999</v>
+        <v>6.466099982999999</v>
       </c>
       <c r="P95">
-        <v>12.0321578715</v>
+        <v>12.008471397</v>
       </c>
       <c r="Q95">
-        <v>12.8321578715</v>
+        <v>12.808471397</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.756565461923652</v>
+        <v>2.031336292230145</v>
       </c>
       <c r="T95">
-        <v>8.40562743596816</v>
+        <v>9.755678790892627</v>
       </c>
       <c r="U95">
         <v>0.0543</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>6.462106301595548</v>
+        <v>6.393360489876445</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1550574775338086</v>
+        <v>0.1543310227329616</v>
       </c>
       <c r="C96">
-        <v>37.26720019360672</v>
+        <v>37.12249812859632</v>
       </c>
       <c r="D96">
-        <v>99.90960019360672</v>
+        <v>100.4359981285963</v>
       </c>
       <c r="E96">
-        <v>55.07340000000001</v>
+        <v>55.74450000000001</v>
       </c>
       <c r="F96">
-        <v>63.0834</v>
+        <v>63.75450000000001</v>
       </c>
       <c r="G96">
         <v>0.441</v>
@@ -9153,28 +9153,28 @@
         <v>21.9</v>
       </c>
       <c r="M96">
-        <v>3.42542862</v>
+        <v>3.461869350000001</v>
       </c>
       <c r="N96">
-        <v>18.47457138</v>
+        <v>18.43813065</v>
       </c>
       <c r="O96">
-        <v>6.466099982999999</v>
+        <v>6.453345727499999</v>
       </c>
       <c r="P96">
-        <v>12.008471397</v>
+        <v>11.9847849225</v>
       </c>
       <c r="Q96">
-        <v>12.808471397</v>
+        <v>12.7847849225</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.031336292230145</v>
+        <v>2.416015454659235</v>
       </c>
       <c r="T96">
-        <v>9.755678790892627</v>
+        <v>11.64575068778688</v>
       </c>
       <c r="U96">
         <v>0.0543</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>6.393360489876445</v>
+        <v>6.326061958404061</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1543310227329616</v>
+        <v>0.1536045679321146</v>
       </c>
       <c r="C97">
-        <v>37.12249812859632</v>
+        <v>36.98337235373688</v>
       </c>
       <c r="D97">
-        <v>100.4359981285963</v>
+        <v>100.9679723537369</v>
       </c>
       <c r="E97">
-        <v>55.74450000000001</v>
+        <v>56.4156</v>
       </c>
       <c r="F97">
-        <v>63.75450000000001</v>
+        <v>64.4256</v>
       </c>
       <c r="G97">
         <v>0.441</v>
@@ -9235,28 +9235,28 @@
         <v>21.9</v>
       </c>
       <c r="M97">
-        <v>3.461869350000001</v>
+        <v>3.49831008</v>
       </c>
       <c r="N97">
-        <v>18.43813065</v>
+        <v>18.40168992</v>
       </c>
       <c r="O97">
-        <v>6.453345727499999</v>
+        <v>6.440591471999999</v>
       </c>
       <c r="P97">
-        <v>11.9847849225</v>
+        <v>11.961098448</v>
       </c>
       <c r="Q97">
-        <v>12.7847849225</v>
+        <v>12.761098448</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.416015454659235</v>
+        <v>2.99303419830287</v>
       </c>
       <c r="T97">
-        <v>11.64575068778688</v>
+        <v>14.48085853312826</v>
       </c>
       <c r="U97">
         <v>0.0543</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>6.326061958404061</v>
+        <v>6.260165479670686</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1536045679321146</v>
+        <v>0.1528781131312676</v>
       </c>
       <c r="C98">
-        <v>36.98337235373685</v>
+        <v>36.84991194780162</v>
       </c>
       <c r="D98">
-        <v>100.9679723537369</v>
+        <v>101.5056119478016</v>
       </c>
       <c r="E98">
-        <v>56.4156</v>
+        <v>57.0867</v>
       </c>
       <c r="F98">
-        <v>64.4256</v>
+        <v>65.0967</v>
       </c>
       <c r="G98">
         <v>0.441</v>
@@ -9317,28 +9317,28 @@
         <v>21.9</v>
       </c>
       <c r="M98">
-        <v>3.49831008</v>
+        <v>3.53475081</v>
       </c>
       <c r="N98">
-        <v>18.40168992</v>
+        <v>18.36524919</v>
       </c>
       <c r="O98">
-        <v>6.440591471999999</v>
+        <v>6.4278372165</v>
       </c>
       <c r="P98">
-        <v>11.961098448</v>
+        <v>11.9374119735</v>
       </c>
       <c r="Q98">
-        <v>12.761098448</v>
+        <v>12.7374119735</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.993034198302863</v>
+        <v>3.954732104375584</v>
       </c>
       <c r="T98">
-        <v>14.48085853312823</v>
+        <v>19.20603827536385</v>
       </c>
       <c r="U98">
         <v>0.0543</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>6.260165479670686</v>
+        <v>6.195627691220475</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1528781131312676</v>
+        <v>0.1521516583304206</v>
       </c>
       <c r="C99">
-        <v>36.84991194780162</v>
+        <v>36.7222078970464</v>
       </c>
       <c r="D99">
-        <v>101.5056119478016</v>
+        <v>102.0490078970464</v>
       </c>
       <c r="E99">
-        <v>57.0867</v>
+        <v>57.7578</v>
       </c>
       <c r="F99">
-        <v>65.0967</v>
+        <v>65.76779999999999</v>
       </c>
       <c r="G99">
         <v>0.441</v>
@@ -9399,28 +9399,28 @@
         <v>21.9</v>
       </c>
       <c r="M99">
-        <v>3.53475081</v>
+        <v>3.57119154</v>
       </c>
       <c r="N99">
-        <v>18.36524919</v>
+        <v>18.32880846</v>
       </c>
       <c r="O99">
-        <v>6.4278372165</v>
+        <v>6.415082960999999</v>
       </c>
       <c r="P99">
-        <v>11.9374119735</v>
+        <v>11.913725499</v>
       </c>
       <c r="Q99">
-        <v>12.7374119735</v>
+        <v>12.713725499</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.954732104375584</v>
+        <v>5.878127916521026</v>
       </c>
       <c r="T99">
-        <v>19.20603827536385</v>
+        <v>28.65639775983507</v>
       </c>
       <c r="U99">
         <v>0.0543</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>6.195627691220475</v>
+        <v>6.132407000493735</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1521516583304206</v>
+        <v>0.1520687035295736</v>
       </c>
       <c r="C100">
-        <v>36.7222078970464</v>
+        <v>36.11352931431227</v>
       </c>
       <c r="D100">
-        <v>102.0490078970464</v>
+        <v>102.1114293143123</v>
       </c>
       <c r="E100">
-        <v>57.7578</v>
+        <v>58.42890000000001</v>
       </c>
       <c r="F100">
-        <v>65.76779999999999</v>
+        <v>66.4389</v>
       </c>
       <c r="G100">
         <v>0.441</v>
@@ -9481,129 +9481,47 @@
         <v>21.9</v>
       </c>
       <c r="M100">
-        <v>3.57119154</v>
+        <v>3.67407117</v>
       </c>
       <c r="N100">
-        <v>18.32880846</v>
+        <v>18.22592883</v>
       </c>
       <c r="O100">
-        <v>6.415082960999999</v>
+        <v>6.379075090499999</v>
       </c>
       <c r="P100">
-        <v>11.913725499</v>
+        <v>11.8468537395</v>
       </c>
       <c r="Q100">
-        <v>12.713725499</v>
+        <v>12.6468537395</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.878127916521026</v>
+        <v>11.64831535295735</v>
       </c>
       <c r="T100">
-        <v>28.65639775983507</v>
+        <v>57.00747621324877</v>
       </c>
       <c r="U100">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V100">
         <v>0.35</v>
       </c>
       <c r="W100">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y100">
-        <v>6.132407000493735</v>
+        <v>5.9606901953399</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1520687035295736</v>
-      </c>
-      <c r="C101">
-        <v>36.11352931431227</v>
-      </c>
-      <c r="D101">
-        <v>102.1114293143123</v>
-      </c>
-      <c r="E101">
-        <v>58.42890000000001</v>
-      </c>
-      <c r="F101">
-        <v>66.4389</v>
-      </c>
-      <c r="G101">
-        <v>0.441</v>
-      </c>
-      <c r="H101">
-        <v>59.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>22.7</v>
-      </c>
-      <c r="K101">
-        <v>0.8000000000000007</v>
-      </c>
-      <c r="L101">
-        <v>21.9</v>
-      </c>
-      <c r="M101">
-        <v>3.67407117</v>
-      </c>
-      <c r="N101">
-        <v>18.22592883</v>
-      </c>
-      <c r="O101">
-        <v>6.379075090499999</v>
-      </c>
-      <c r="P101">
-        <v>11.8468537395</v>
-      </c>
-      <c r="Q101">
-        <v>12.6468537395</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.64831535295735</v>
-      </c>
-      <c r="T101">
-        <v>57.00747621324877</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.35</v>
-      </c>
-      <c r="W101">
-        <v>0.035945</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.9606901953399</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
